--- a/MI_PE_Tracking_System.xlsx
+++ b/MI_PE_Tracking_System.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28560" windowHeight="20920" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Master Log MI_PE" sheetId="1" state="visible" r:id="rId1"/>
@@ -32,38 +32,38 @@
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
       <i val="1"/>
       <color rgb="FF6B7280"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,16 +90,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,11 +127,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -134,25 +167,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,15 +196,60 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,2067 +509,3230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7421875" defaultRowHeight="15"/>
+  <dimension ref="A1:N61"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.609375" defaultRowHeight="15"/>
   <cols>
-    <col width="13.98828125" customWidth="1" min="1" max="1"/>
-    <col width="11.02734375" customWidth="1" min="2" max="2"/>
-    <col width="9.01171875" customWidth="1" min="3" max="3"/>
-    <col width="11.02734375" customWidth="1" min="4" max="4"/>
-    <col width="9.01171875" customWidth="1" min="5" max="5"/>
-    <col width="11.02734375" customWidth="1" min="6" max="7"/>
-    <col width="37.93359375" customWidth="1" min="8" max="11"/>
-    <col width="32.015625" customWidth="1" min="12" max="13"/>
-    <col width="37.93359375" customWidth="1" min="14" max="14"/>
+    <col width="13.98828125" customWidth="1" style="37" min="1" max="1"/>
+    <col width="11.02734375" customWidth="1" style="37" min="2" max="2"/>
+    <col width="9.01171875" customWidth="1" style="37" min="3" max="3"/>
+    <col width="11.02734375" customWidth="1" style="37" min="4" max="4"/>
+    <col width="9.01171875" customWidth="1" style="37" min="5" max="5"/>
+    <col width="11.02734375" customWidth="1" style="37" min="6" max="7"/>
+    <col width="37.93359375" customWidth="1" style="37" min="8" max="11"/>
+    <col width="32.015625" customWidth="1" style="37" min="12" max="13"/>
+    <col width="37.93359375" customWidth="1" style="37" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="37">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>MARKET INTELLIGENCE &amp; PRIVATE EQUITY TRACKING SYSTEM</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Last Updated: July 2, 2026 | Continuous Apr 20 -&gt; Jul 2 via loop workflow; May 6-Jun 4 backfilled (verified milestones)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>Last Updated: July 21, 2026 | Continuous Apr 20 -&gt; Jul 21; May 6-Jun 4 + Jun 8-16 + Jul 3-21 filled (verified/derived flagged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="37">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>S&amp;P Δ%</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>Nasdaq</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>Nasdaq Δ%</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>WTI Crude</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>Brent Crude</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>AI / Tech Signal</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t>M&amp;A / PE Signal</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" s="31" t="inlineStr">
         <is>
           <t>Healthcare Signal</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t>Defense Signal</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="31" t="inlineStr">
         <is>
           <t>Oil Signal</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t>Key Macro Theme</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="75" customHeight="1" s="37">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Apr 20 2026</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="24" t="n">
         <v>7109.14</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="25" t="n">
         <v>-0.0024</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="24" t="n">
         <v>24404.39</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="25" t="n">
         <v>-0.0026</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="26" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="26" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>Nasdaq snaps 13-day winning streak (longest since 1992)</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>Middle-market M&amp;A optimism; 58% execs expect volume to climb</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t>Biopharma M&amp;A Q1: $15.6B across 19 deals; 6 IPOs raised $1.8B</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>Pentagon $350B reconciliation budget request</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>Brent ~$96; ~$29 rise YoY; geopolitical premium intact</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t>Market consolidation after 13-day run; geopolitical premium in oil</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t>Nasdaq 13-day streak ended; longest positive streak since 1992.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="75" customHeight="1" s="37">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Apr 22 2026</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="24" t="n">
         <v>7137.9</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="25" t="n">
         <v>0.0105</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="24" t="n">
         <v>24657.57</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="25" t="n">
         <v>0.0164</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="26" t="n">
         <v>96.5</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>Nasdaq hits new all-time intraday high; AI/chip strength leads</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>PE dry powder deploying; secondary transactions dominant exit route</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t>Medtech VC: $2.2B across 66 rounds Q1 2026</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>Raytheon Zumwalt integration contract; UK Defense Plan delayed</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>Oil elevated on geopolitical tensions; ME risk premium</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="23" t="inlineStr">
         <is>
           <t>Broad market recovery; AI and semis lead</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t>S&amp;P +1.05%, Nasdaq +1.64%. Nasdaq new ATH intraday.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="75" customHeight="1" s="37">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Apr 23 2026</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="24" t="n">
         <v>7108.4</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="25" t="n">
         <v>-0.0041</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="24" t="n">
         <v>24438.5</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="25" t="n">
         <v>-0.0089</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="26" t="n">
         <v>95.5</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Arm Holdings CEO Rene Haas featured; chip sector digesting gains</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>Blackstone closes largest private life sciences fund ever at $6.3B (BXLS VI)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>FDA approved Otarmeni — first gene therapy for rare hearing loss</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>Peru selects Lockheed F-16 Block 70 over European rivals</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>Slight pullback as US-Iran talk optimism tempers energy bid</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>Slight pullback; profit-taking after ATH</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t>S&amp;P -0.41%, Nasdaq -0.89%. Dow -179.71pts.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="75" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="75" customHeight="1" s="37">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Apr 24 2026</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="24" t="n">
         <v>7165.08</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="25" t="n">
         <v>0.008</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="24" t="n">
         <v>24836.6</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="25" t="n">
         <v>0.0163</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="26" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="26" t="n">
         <v>105.33</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>S&amp;P &amp; Nasdaq both close at record highs; AMD +45% in April; Intel rally</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>Hologic acquired by Blackstone/TPG — $18.3B EV closed Apr 7</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t>Regeneron strikes private pricing deal w/ Trump; $27B US drug pledge</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>Boeing MQ-25 Stingray first flight imminent; Navy spending plan updated</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t>WTI &lt;$94 on US-Iran diplomacy; Brent $105.33</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="23" t="inlineStr">
         <is>
           <t>Record highs driven by AI/chip strength; US-Iran peace talk optimism</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t>S&amp;P record 7,165. Nasdaq record 24,837. AMD +45% MTD.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="75" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="75" customHeight="1" s="37">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Apr 25 2026</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="24" t="n">
         <v>7165</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="24" t="n">
         <v>24837</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="26" t="n">
         <v>94.04000000000001</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="26" t="n">
         <v>105.33</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>AI stocks and Intel rally lift Wall St to record; GPT-5.5 released by OpenAI</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>PE dealmaking reviving on ME de-escalation; Affinity/EA LBO scrutiny</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>14 drugmakers struck price agreements w/ Trump (Pfizer, Lilly, GSK, Boehringer)</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>FY27 budget: Air Force/Space Force $338.8B record; 38 F-35s ($7.4B)</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>WTI ~$94; Brent ~$105; MTD +3%; YoY +60%</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="23" t="inlineStr">
         <is>
           <t>Record close; AI super app vision (GPT-5.5); US-Iran optimism</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t>S&amp;P record 7,165. April MTD +9.8%.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="75" customHeight="1" s="37">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Apr 26 2026</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="24" t="n">
         <v>7165</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="24" t="n">
         <v>24837</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="26" t="n">
         <v>93.68000000000001</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="26" t="n">
         <v>105.2</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>DeepSeek Hybrid Attention + 1M token context; Meta capex $115-135B for AI</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>PE momentum building on US-Iran de-escalation (Blackstone Baratta)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>Stellus Rx acquires Tria Health (WindRose); Sanofi/Dynavax $2.2B closing Q1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>Northrop Grumman delivered first EGI-M airborne nav system; Saab 20 Gripens/yr</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>WTI ~$94 (-0.38%); Brent ~$105; geopolitical premium easing</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>4th consecutive weekly gain; S&amp;P April MTD +9.8%; AI concentration accelerating</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t>S&amp;P 4th consecutive weekly gain. April +9.8%.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="75" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="75" customHeight="1" s="37">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Apr 27 2026</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="28" t="n">
         <v>7138.8</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="29" t="n">
         <v>-0.0049</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="28" t="n">
         <v>24663.8</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="29" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="30" t="n">
         <v>95.5</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="30" t="n">
         <v>107</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>OpenAI growth concerns surface; WSJ reports CFO Friar warned on compute payments</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Apollo acquiring Forvia auto interiors $2.1B; Sun Pharma/Organon $11.75B</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="27" t="inlineStr">
         <is>
           <t>Coca-Cola +4% on earnings beat (defensive bid)</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t>Blackstone consortium agreed £1.4B (~$1.9B) take-private of Senior plc (UK aero/def)</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" s="27" t="inlineStr">
         <is>
           <t>Oil pressure equities; Strait of Hormuz risk premium back</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>Pullback on OpenAI report + oil; defensive rotation (Coke beat)</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" s="27" t="inlineStr">
         <is>
           <t>S&amp;P -0.49%, Nasdaq -0.90%. OpenAI/Oracle optics weighed on AI sector.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12" ht="75" customHeight="1" s="37">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Apr 28 2026</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="28" t="n">
         <v>7173.91</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="29" t="n">
         <v>0.0049</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="28" t="n">
         <v>24887</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="29" t="n">
         <v>0.0091</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="30" t="n">
         <v>96</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="30" t="n">
         <v>108</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Nvidia +4%, Alphabet +1.8%, Micron +5.6%; Apple -1.3%; Mag7 reports begin Apr 29</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Apollo/Forvia close; Sun Pharma/Organon $11.75B; Senior plc takeover advancing</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>J&amp;J/Atraverse Medical acquisition (Apr 24)</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K12" s="27" t="inlineStr">
         <is>
           <t>Senior plc £1.4B (Blackstone consortium); Pentagon $60B AI request FY27</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L12" s="27" t="inlineStr">
         <is>
           <t>WTI ~$96; Brent ~$108; Iran ceasefire intact but fragile</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t>S&amp;P record 7,173.91; Nasdaq fresh high; pre-earnings caution</t>
         </is>
       </c>
-      <c r="N12" s="6" t="inlineStr">
+      <c r="N12" s="27" t="inlineStr">
         <is>
           <t>S&amp;P fresh ATH 7,173.91. Hyperscaler capex ~$700B in 2026.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="75" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13" ht="75" customHeight="1" s="37">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Apr 29 2026</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="28" t="n">
         <v>7135.95</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="29" t="n">
         <v>-0.0053</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="28" t="n">
         <v>24795</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="29" t="n">
         <v>-0.0037</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="30" t="n">
         <v>96.5</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="30" t="n">
         <v>108.5</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Mag7 earnings begin; AI capex commentary watched closely</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>PE Q1 deal value $154.6B (+12.6% YoY); 22 transactions &gt;$10B</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="27" t="inlineStr">
         <is>
           <t>Pfizer beats Q1 EPS; reaffirms 2026 outlook ($59.5-62.5B revenue)</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K13" s="27" t="inlineStr">
         <is>
           <t>Defense spending visibility on FY27 Pentagon $1.15T base request</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="27" t="inlineStr">
         <is>
           <t>Oil firming on supply-side concerns</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Fed split vote leaves H2 cut timing unresolved; 10Y to 4.41%; Dow -280pts</t>
         </is>
       </c>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="N13" s="27" t="inlineStr">
         <is>
           <t>S&amp;P -0.53%, Nasdaq -0.37%. Fed pause posture pressures rate-sensitives.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="75" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14" ht="75" customHeight="1" s="37">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Apr 30 2026</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="28" t="n">
         <v>7155</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="29" t="n">
         <v>0.0027</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="28" t="n">
         <v>24850</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="29" t="n">
         <v>0.0022</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="30" t="n">
         <v>95.8</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="30" t="n">
         <v>107.8</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Apple report after-close; AI capex commentary in focus</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Goldman raises S&amp;P target to 7,600 on 12% EPS growth + AI capex tailwind</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J14" s="27" t="inlineStr">
         <is>
           <t>April biotech M&amp;A momentum continues</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t>FY27 budget detail emerging on aerospace primes</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="L14" s="27" t="inlineStr">
         <is>
           <t>Oil softening on diplomacy progress</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>Apple report; April MTD ~+10% (best month since 2020)</t>
         </is>
       </c>
-      <c r="N14" s="6" t="inlineStr">
+      <c r="N14" s="27" t="inlineStr">
         <is>
           <t>April closes ~+10% (best month since 2020). Q1 GDP +2.0%.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="75" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15" ht="75" customHeight="1" s="37">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>May 1 2026</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="28" t="n">
         <v>7230.12</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="29" t="n">
         <v>0.0105</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="28" t="n">
         <v>25114.44</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="29" t="n">
         <v>0.0107</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="30" t="n">
         <v>95</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="30" t="n">
         <v>107</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Goldman target 7,600; AI capex ~$670B across hyperscalers</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Q1 PE M&amp;A: 614 deals/$154.6B; 22 deals &gt;$10B (record); buybacks $422B YTD</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" s="27" t="inlineStr">
         <is>
           <t>Pfizer Q1 beat; 14 drugmakers Trump pricing deals advancing</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K15" s="27" t="inlineStr">
         <is>
           <t>Senior plc deal close-watch; FY27 Pentagon $1.5T request</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="L15" s="27" t="inlineStr">
         <is>
           <t>WTI ~$95; Brent ~$107; ceasefire fragile</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>S&amp;P ATH 7,230.12; best monthly return since April 2020</t>
         </is>
       </c>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="N15" s="27" t="inlineStr">
         <is>
           <t>S&amp;P ATH 7,230.12. Nasdaq ATH 25,114.44. April best month since 2020.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="75" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16" ht="75" customHeight="1" s="37">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>May 4 2026</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="28" t="n">
         <v>7200.75</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="29" t="n">
         <v>-0.0041</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="28" t="n">
         <v>25067</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="29" t="n">
         <v>-0.0019</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="30" t="n">
         <v>102.27</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="30" t="n">
         <v>109.87</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Palantir -3% post-earnings beat; Pinterest +15% on Q2 guide</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Wiz/Alphabet $32B all-cash advancing (FTC Ferguson test case)</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J16" s="27" t="inlineStr">
         <is>
           <t>Pfizer continued strength post-Q1</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K16" s="27" t="inlineStr">
         <is>
           <t>UAE missile intercept; US response to Iran small boats; Hegseth on Hormuz</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L16" s="27" t="inlineStr">
         <is>
           <t>Oil spikes on UAE intercept + Strait of Hormuz tensions</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>Risk-off; UAE missile intercept; geopolitical premium back</t>
         </is>
       </c>
-      <c r="N16" s="6" t="inlineStr">
+      <c r="N16" s="27" t="inlineStr">
         <is>
           <t>S&amp;P -0.41%. Energy only sector green; materials -1.57%.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="75" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17" ht="75" customHeight="1" s="37">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>May 5 2026</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="33" t="n">
         <v>7259.22</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="34" t="n">
         <v>0.0081</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="33" t="n">
         <v>25326.13</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="34" t="n">
         <v>0.0103</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="35" t="n">
         <v>102.27</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="35" t="n">
         <v>109.87</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="32" t="inlineStr">
         <is>
           <t>Micron +10% (&gt;$700B mkt cap; HBM sold out 2026); Nvidia $199.25</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="32" t="inlineStr">
         <is>
           <t>Devon upgrade to strong buy by RBC; $72 PT (post-Coterra merger)</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J17" s="32" t="inlineStr">
         <is>
           <t>Pfizer +2.2% (Q1 beat reaffirmed)</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K17" s="32" t="inlineStr">
         <is>
           <t>Hegseth: US wants Iran deal; Strait of Hormuz strategic priority</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="L17" s="32" t="inlineStr">
         <is>
           <t>WTI -3.9% to $102.27; Brent -3.99% to $109.87; oil-down/equities-up correlation</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" s="32" t="inlineStr">
         <is>
           <t>S&amp;P fresh ATH 7,259.22; Nasdaq ATH; Russell 2000 intraday ATH; VIX -6.8%</t>
         </is>
       </c>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N17" s="32" t="inlineStr">
         <is>
           <t>S&amp;P ATH 7,259.22. Nasdaq ATH 25,326.13. Oil -10% drove broad rally.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+    <row r="18" ht="36" customHeight="1" s="37">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>May 6 2026</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="20" t="n">
         <v>7365.12</v>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="20" t="n">
         <v>0.0146</v>
       </c>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="inlineStr">
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>Tech steady</t>
         </is>
       </c>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>PE deploying into rebound</t>
         </is>
       </c>
-      <c r="J18" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" s="27" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>Oil eases on US-Iran deal hopes</t>
         </is>
       </c>
-      <c r="M18" s="27" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>US-Iran nearing war-end deal</t>
         </is>
       </c>
-      <c r="N18" s="27" t="inlineStr">
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>S&amp;P +1.46%; report of imminent Iran agreement</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+    <row r="19" ht="36" customHeight="1" s="37">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>May 11 2026</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="20" t="n">
         <v>7412</v>
       </c>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>AI leadership continues</t>
         </is>
       </c>
-      <c r="I19" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="27" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>New all-time high</t>
         </is>
       </c>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="N19" s="20" t="inlineStr">
         <is>
           <t>S&amp;P ATH ~7,412 (breaks above 7,400)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="20" ht="36" customHeight="1" s="37">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>May 14 2026</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="20" t="n">
         <v>7501.39</v>
       </c>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="inlineStr">
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>Chip/AI strength</t>
         </is>
       </c>
-      <c r="I20" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K20" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="27" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>First close above 7,500</t>
         </is>
       </c>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>New record 7,501.39</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+    <row r="21" ht="36" customHeight="1" s="37">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>May 25 2026</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="n"/>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="n"/>
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="40" t="inlineStr">
+        <is>
+          <t>Memorial Day holiday</t>
+        </is>
+      </c>
+      <c r="N21" s="40" t="inlineStr">
+        <is>
+          <t>Markets closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="37">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>May 27 2026</t>
         </is>
       </c>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
-      <c r="H21" s="27" t="inlineStr">
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>Micron joins $1T market-cap club</t>
         </is>
       </c>
-      <c r="I21" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K21" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="27" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>S&amp;P all-time high</t>
         </is>
       </c>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>Micron $1T; record close</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+    <row r="23" ht="36" customHeight="1" s="37">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>May 28 2026</t>
         </is>
       </c>
-      <c r="B22" s="27" t="n">
+      <c r="B23" s="20" t="n">
         <v>7599.96</v>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C23" s="20" t="n">
         <v>0.0026</v>
       </c>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
-      <c r="H22" s="27" t="inlineStr">
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>AI rally broadens</t>
         </is>
       </c>
-      <c r="I22" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K22" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="27" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>Approaching 7,600</t>
         </is>
       </c>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>Record 7,599.96 (+0.26%)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+    <row r="24" ht="36" customHeight="1" s="37">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>May 29 2026</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n">
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n">
         <v>26972.62</v>
       </c>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
-      <c r="H23" s="27" t="inlineStr">
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>Nasdaq intraday high 26,972.62</t>
         </is>
       </c>
-      <c r="I23" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="27" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>Month-end record highs</t>
         </is>
       </c>
-      <c r="N23" s="27" t="inlineStr">
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>All 3 indexes record; Nasdaq +~16% YTD</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+    <row r="25" ht="36" customHeight="1" s="37">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Jun 1 2026</t>
         </is>
       </c>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
-      <c r="H24" s="27" t="inlineStr">
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Tech rally overpowers oil spike</t>
         </is>
       </c>
-      <c r="I24" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L24" s="27" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>Brent peaked &gt;$113 in May on Hormuz disruption</t>
         </is>
       </c>
-      <c r="M24" s="27" t="inlineStr">
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>First close above 7,600</t>
         </is>
       </c>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>S&amp;P crosses 7,600 first time (CNBC Jun 1)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+    <row r="26" ht="36" customHeight="1" s="37">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Jun 2 2026</t>
         </is>
       </c>
-      <c r="B25" s="27" t="n">
+      <c r="B26" s="21" t="n">
         <v>7609.78</v>
       </c>
-      <c r="C25" s="27" t="n">
+      <c r="C26" s="21" t="n">
         <v>0.0013</v>
       </c>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
-      <c r="H25" s="27" t="inlineStr">
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>AI/chip melt-up</t>
         </is>
       </c>
-      <c r="I25" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L25" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="27" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>Record; Goldman 7,600 target met early</t>
         </is>
       </c>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="N26" s="21" t="inlineStr">
         <is>
           <t>Record close 7,609.78</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+    <row r="27" ht="36" customHeight="1" s="37">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>Jun 4 2026</t>
+        </is>
+      </c>
+      <c r="B27" s="40" t="n">
+        <v>7583.95</v>
+      </c>
+      <c r="C27" s="40" t="n"/>
+      <c r="D27" s="40" t="n"/>
+      <c r="E27" s="40" t="n"/>
+      <c r="F27" s="40" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="40" t="inlineStr">
+        <is>
+          <t>Near-record into chip rout</t>
+        </is>
+      </c>
+      <c r="I27" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="40" t="inlineStr">
+        <is>
+          <t>Eve of air-pocket #1</t>
+        </is>
+      </c>
+      <c r="N27" s="40" t="inlineStr">
+        <is>
+          <t>Derived from Jun 5 −2.64% print</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" s="37">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Jun 5 2026</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B28" s="21" t="n">
         <v>7383.74</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C28" s="21" t="n">
         <v>-0.0264</v>
       </c>
-      <c r="D26" s="28" t="n"/>
-      <c r="E26" s="28" t="n"/>
-      <c r="F26" s="28" t="n">
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n">
         <v>93.45</v>
       </c>
-      <c r="G26" s="28" t="n">
+      <c r="G28" s="21" t="n">
         <v>97.44</v>
       </c>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>Chip rout: SOX -10.3% (worst since 2020) on Broadcom soft guide</t>
         </is>
       </c>
-      <c r="I26" s="28" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>Apollo/Blackstone $36B private-credit funds Anthropic TPU deal (May 29)</t>
         </is>
       </c>
-      <c r="J26" s="28" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>Parabilis Medicines IPO up to $475M</t>
         </is>
       </c>
-      <c r="K26" s="28" t="inlineStr">
+      <c r="K28" s="21" t="inlineStr">
         <is>
           <t>Lockheed $1B+ contracts</t>
         </is>
       </c>
-      <c r="L26" s="28" t="inlineStr">
+      <c r="L28" s="21" t="inlineStr">
         <is>
           <t>WTI $93.45 / Brent $97.44; premium fading</t>
         </is>
       </c>
-      <c r="M26" s="28" t="inlineStr">
+      <c r="M28" s="21" t="inlineStr">
         <is>
           <t>AI air-pocket #1; hot May jobs 172k</t>
         </is>
       </c>
-      <c r="N26" s="28" t="inlineStr">
+      <c r="N28" s="21" t="inlineStr">
         <is>
           <t>Worst day since Oct 2025</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+    <row r="29" ht="36" customHeight="1" s="37">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>Jun 8 2026</t>
+        </is>
+      </c>
+      <c r="B29" s="40" t="n">
+        <v>7405.73</v>
+      </c>
+      <c r="C29" s="40" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D29" s="40" t="n"/>
+      <c r="E29" s="40" t="n"/>
+      <c r="F29" s="40" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="40" t="inlineStr">
+        <is>
+          <t>Chip rebound fails to hold</t>
+        </is>
+      </c>
+      <c r="I29" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="40" t="inlineStr">
+        <is>
+          <t>Post-rout stabilization</t>
+        </is>
+      </c>
+      <c r="N29" s="40" t="inlineStr">
+        <is>
+          <t>FRED-sourced close</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="37">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>Jun 9 2026</t>
+        </is>
+      </c>
+      <c r="B30" s="40" t="n">
+        <v>7386.65</v>
+      </c>
+      <c r="C30" s="40" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="40" t="inlineStr">
+        <is>
+          <t>Chip surge loses momentum</t>
+        </is>
+      </c>
+      <c r="I30" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="40" t="inlineStr">
+        <is>
+          <t>Oil pulls back</t>
+        </is>
+      </c>
+      <c r="N30" s="40" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="37">
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>Jun 10 2026</t>
+        </is>
+      </c>
+      <c r="B31" s="40" t="n">
+        <v>7266.99</v>
+      </c>
+      <c r="C31" s="40" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="40" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="40" t="inlineStr">
+        <is>
+          <t>Selloff deepens</t>
+        </is>
+      </c>
+      <c r="I31" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L31" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="40" t="inlineStr">
+        <is>
+          <t>Worst day of the June pullback</t>
+        </is>
+      </c>
+      <c r="N31" s="40" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="37">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>Jun 11 2026</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="n">
+        <v>7394.3</v>
+      </c>
+      <c r="C32" s="40" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="D32" s="40" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="40" t="inlineStr">
+        <is>
+          <t>Sharp rebound</t>
+        </is>
+      </c>
+      <c r="I32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="40" t="inlineStr">
+        <is>
+          <t>Dip-buying returns</t>
+        </is>
+      </c>
+      <c r="N32" s="40" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="37">
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>Jun 12 2026</t>
+        </is>
+      </c>
+      <c r="B33" s="40" t="n">
+        <v>7431.46</v>
+      </c>
+      <c r="C33" s="40" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D33" s="40" t="n"/>
+      <c r="E33" s="40" t="n"/>
+      <c r="F33" s="40" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="40" t="inlineStr">
+        <is>
+          <t>Recovery extends</t>
+        </is>
+      </c>
+      <c r="I33" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="40" t="inlineStr">
+        <is>
+          <t>Two-day rebound</t>
+        </is>
+      </c>
+      <c r="N33" s="40" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="37">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>Jun 15 2026</t>
+        </is>
+      </c>
+      <c r="B34" s="40" t="n">
+        <v>7554.29</v>
+      </c>
+      <c r="C34" s="40" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="D34" s="40" t="n"/>
+      <c r="E34" s="40" t="n"/>
+      <c r="F34" s="40" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="40" t="inlineStr">
+        <is>
+          <t>SpaceX rally extends</t>
+        </is>
+      </c>
+      <c r="I34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="40" t="inlineStr">
+        <is>
+          <t>Trump announces US-Iran war-end agreement; best day since April; oil sinks</t>
+        </is>
+      </c>
+      <c r="N34" s="40" t="inlineStr">
+        <is>
+          <t>CNBC/247WallSt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="37">
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>Jun 16 2026</t>
+        </is>
+      </c>
+      <c r="B35" s="40" t="n">
+        <v>7510.98</v>
+      </c>
+      <c r="C35" s="40" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="40" t="inlineStr">
+        <is>
+          <t>Warsh first-meeting jitters</t>
+        </is>
+      </c>
+      <c r="I35" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="40" t="inlineStr">
+        <is>
+          <t>Bond-yield surge; Dow −500</t>
+        </is>
+      </c>
+      <c r="N35" s="40" t="inlineStr">
+        <is>
+          <t>Derived from Jun 17 −1.21% print</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="37">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Jun 17 2026</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B36" s="21" t="n">
         <v>7420.1</v>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C36" s="21" t="n">
         <v>-0.0121</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D36" s="21" t="n">
         <v>26021.66</v>
       </c>
-      <c r="E27" s="28" t="n">
+      <c r="E36" s="21" t="n">
         <v>-0.0134</v>
       </c>
-      <c r="F27" s="28" t="n"/>
-      <c r="G27" s="28" t="n"/>
-      <c r="H27" s="28" t="inlineStr">
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>Chips slide into Fed day</t>
         </is>
       </c>
-      <c r="I27" s="28" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr">
         <is>
           <t>Mega-LBO barbell (EA $55B, WBA $23.7B, OneStream $6.4B)</t>
         </is>
       </c>
-      <c r="J27" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K27" s="28" t="inlineStr">
+      <c r="J36" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="21" t="inlineStr">
         <is>
           <t>Iran war sustains demand</t>
         </is>
       </c>
-      <c r="L27" s="28" t="inlineStr">
+      <c r="L36" s="21" t="inlineStr">
         <is>
           <t>10Y 4.46%</t>
         </is>
       </c>
-      <c r="M27" s="28" t="inlineStr">
+      <c r="M36" s="21" t="inlineStr">
         <is>
           <t>FED REGIME CHANGE: Warsh; 9/18 project HIKE</t>
         </is>
       </c>
-      <c r="N27" s="28" t="inlineStr">
+      <c r="N36" s="21" t="inlineStr">
         <is>
           <t>Worst new-Chair Fed-day since 1994</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="37" ht="36" customHeight="1" s="37">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Jun 18 2026</t>
         </is>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B37" s="21" t="n">
         <v>7500.58</v>
       </c>
-      <c r="C28" s="28" t="n">
+      <c r="C37" s="21" t="n">
         <v>0.0108</v>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D37" s="21" t="n">
         <v>26412</v>
       </c>
-      <c r="E28" s="28" t="n">
+      <c r="E37" s="21" t="n">
         <v>0.015</v>
       </c>
-      <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="21" t="n"/>
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Chips fuel comeback</t>
         </is>
       </c>
-      <c r="I28" s="28" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>Take-privates continue</t>
         </is>
       </c>
-      <c r="J28" s="28" t="inlineStr">
+      <c r="J37" s="21" t="inlineStr">
         <is>
           <t>Biotech IPO window ajar</t>
         </is>
       </c>
-      <c r="K28" s="28" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>US ends Iran blockade</t>
         </is>
       </c>
-      <c r="L28" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="28" t="inlineStr">
+      <c r="L37" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="21" t="inlineStr">
         <is>
           <t>Recovery; Russell 2000 up</t>
         </is>
       </c>
-      <c r="N28" s="28" t="inlineStr">
+      <c r="N37" s="21" t="inlineStr">
         <is>
           <t>Nasdaq derived +1.5%</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="38" ht="36" customHeight="1" s="37">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Jun 19 2026</t>
         </is>
       </c>
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="E29" s="28" t="n"/>
-      <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="n"/>
-      <c r="H29" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K29" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="28" t="inlineStr">
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="21" t="n"/>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="21" t="inlineStr">
         <is>
           <t>Juneteenth holiday</t>
         </is>
       </c>
-      <c r="N29" s="28" t="inlineStr">
+      <c r="N38" s="21" t="inlineStr">
         <is>
           <t>Markets closed</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+    <row r="39" ht="36" customHeight="1" s="37">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Jun 20 2026</t>
         </is>
       </c>
-      <c r="B30" s="28" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="28" t="n">
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n">
         <v>77.54000000000001</v>
       </c>
-      <c r="G30" s="28" t="n">
+      <c r="G39" s="21" t="n">
         <v>80.56999999999999</v>
       </c>
-      <c r="H30" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K30" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L30" s="28" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
         <is>
           <t>Iran re-closed Hormuz; Israel-Hezbollah ceasefire (tentative)</t>
         </is>
       </c>
-      <c r="M30" s="28" t="inlineStr">
+      <c r="M39" s="21" t="inlineStr">
         <is>
           <t>Oil whipsaw</t>
         </is>
       </c>
-      <c r="N30" s="28" t="inlineStr">
+      <c r="N39" s="21" t="inlineStr">
         <is>
           <t>Weekend geopolitics</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Jun 22 2026</t>
         </is>
       </c>
-      <c r="B31" s="28" t="n">
+      <c r="B40" t="n">
         <v>7509</v>
       </c>
-      <c r="C31" s="28" t="n">
+      <c r="C40" t="n">
         <v>0.0012</v>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D40" t="n">
         <v>26341</v>
       </c>
-      <c r="E31" s="28" t="n">
+      <c r="E40" t="n">
         <v>-0.0027</v>
       </c>
-      <c r="F31" s="28" t="n">
+      <c r="F40" t="n">
         <v>74.3</v>
       </c>
-      <c r="G31" s="28" t="n">
+      <c r="G40" t="n">
         <v>78.41</v>
       </c>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Nasdaq-100 rebalance: CoreWeave+Rocket Lab added, fell</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Montagu/BMC Helix; NextEra/Caliber $1.3B+Quantum JV</t>
         </is>
       </c>
-      <c r="J31" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K31" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L31" s="28" t="inlineStr">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Premium draining; VP Vance 'good foundation'</t>
         </is>
       </c>
-      <c r="M31" s="28" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Dow +0.44%</t>
         </is>
       </c>
-      <c r="N31" s="28" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Post-Juneteenth reopen</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Jun 23 2026</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n">
+      <c r="B41" t="n">
         <v>7365.46</v>
       </c>
-      <c r="C32" s="28" t="n">
+      <c r="C41" t="n">
         <v>-0.0144</v>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D41" t="n">
         <v>25587.04</v>
       </c>
-      <c r="E32" s="28" t="n">
+      <c r="E41" t="n">
         <v>-0.0221</v>
       </c>
-      <c r="F32" s="28" t="n">
+      <c r="F41" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="G32" s="28" t="n">
+      <c r="G41" t="n">
         <v>78</v>
       </c>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>SMH -6.5%; S&amp;P Tech -4.13%; KOSPI -9.99% (air-pocket #2)</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>BofA: 3 Fed hikes 2026 -&gt;4.25-4.50%</t>
         </is>
       </c>
-      <c r="J32" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="28" t="inlineStr">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>War de-escalating</t>
         </is>
       </c>
-      <c r="L32" s="28" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>US Treasury 60-day Iran oil waiver; 67M bbls</t>
         </is>
       </c>
-      <c r="M32" s="28" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>BofA hawkish shock + chip rout</t>
         </is>
       </c>
-      <c r="N32" s="28" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Dow -0.09%</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="28" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Jun 24 2026</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B42" t="n">
         <v>7358.22</v>
       </c>
-      <c r="C33" s="28" t="n">
+      <c r="C42" t="n">
         <v>-0.001</v>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D42" t="n">
         <v>25476.64</v>
       </c>
-      <c r="E33" s="28" t="n">
+      <c r="E42" t="n">
         <v>-0.0043</v>
       </c>
-      <c r="F33" s="28" t="n"/>
-      <c r="G33" s="28" t="n"/>
-      <c r="H33" s="28" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Chips slide ahead of Micron</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K33" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L33" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M33" s="28" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>Dow +0.35% (defensive rotation)</t>
         </is>
       </c>
-      <c r="N33" s="28" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Micron reports after close</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Jun 25 2026</t>
         </is>
       </c>
-      <c r="B34" s="28" t="n">
+      <c r="B43" t="n">
         <v>7357.49</v>
       </c>
-      <c r="C34" s="28" t="n">
+      <c r="C43" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="D34" s="28" t="n">
+      <c r="D43" t="n">
         <v>25358.6</v>
       </c>
-      <c r="E34" s="28" t="n">
+      <c r="E43" t="n">
         <v>-0.0046</v>
       </c>
-      <c r="F34" s="28" t="n"/>
-      <c r="G34" s="28" t="n"/>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Tech soft</t>
         </is>
       </c>
-      <c r="I34" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L34" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="28" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>Dow +0.14%</t>
         </is>
       </c>
-      <c r="N34" s="28" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Flat S&amp;P</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="28" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Jun 26 2026</t>
         </is>
       </c>
-      <c r="B35" s="28" t="n"/>
-      <c r="C35" s="28" t="n"/>
-      <c r="D35" s="28" t="n"/>
-      <c r="E35" s="28" t="n"/>
-      <c r="F35" s="28" t="n">
+      <c r="F44" t="n">
         <v>69.5</v>
       </c>
-      <c r="G35" s="28" t="n"/>
-      <c r="H35" s="28" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Tread water amid tech sell-off</t>
         </is>
       </c>
-      <c r="I35" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K35" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L35" s="28" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>WTI below $70 after cargo-ship attack near Oman</t>
         </is>
       </c>
-      <c r="M35" s="28" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Oil resumes losses</t>
         </is>
       </c>
-      <c r="N35" s="28" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Exact close n/d</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="28" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Jun 29 2026</t>
         </is>
       </c>
-      <c r="B36" s="28" t="n">
+      <c r="B45" t="n">
         <v>7445</v>
       </c>
-      <c r="C36" s="28" t="n">
+      <c r="C45" t="n">
         <v>0.012</v>
       </c>
-      <c r="D36" s="28" t="n"/>
-      <c r="E36" s="28" t="n">
+      <c r="E45" t="n">
         <v>0.02</v>
       </c>
-      <c r="F36" s="28" t="n"/>
-      <c r="G36" s="28" t="n">
+      <c r="G45" t="n">
         <v>73.17</v>
       </c>
-      <c r="H36" s="28" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Nasdaq +2% rebound</t>
         </is>
       </c>
-      <c r="I36" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K36" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L36" s="28" t="inlineStr">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>Renewed US-Iran strikes; Brent $73.17</t>
         </is>
       </c>
-      <c r="M36" s="28" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Dow &gt;52,000 first time</t>
         </is>
       </c>
-      <c r="N36" s="28" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>S&amp;P level derived (+1.2%)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="28" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Jun 30 2026</t>
         </is>
       </c>
-      <c r="B37" s="28" t="n">
+      <c r="B46" t="n">
         <v>7449.36</v>
       </c>
-      <c r="C37" s="28" t="n">
+      <c r="C46" t="n">
         <v>0.0003</v>
       </c>
-      <c r="D37" s="28" t="n">
+      <c r="D46" t="n">
         <v>26213.72</v>
       </c>
-      <c r="E37" s="28" t="n">
+      <c r="E46" t="n">
         <v>0.0029</v>
       </c>
-      <c r="F37" s="28" t="n"/>
-      <c r="G37" s="28" t="n"/>
-      <c r="H37" s="28" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Nasdaq +0.29%</t>
         </is>
       </c>
-      <c r="I37" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M37" s="28" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>Best quarter since 2020</t>
         </is>
       </c>
-      <c r="N37" s="28" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Q2 close</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="28" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Jul 1 2026</t>
         </is>
       </c>
-      <c r="B38" s="28" t="n">
+      <c r="B47" t="n">
         <v>7483</v>
       </c>
-      <c r="C38" s="28" t="n">
+      <c r="C47" t="n">
         <v>0.0045</v>
       </c>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n">
+      <c r="F47" t="n">
         <v>68.58</v>
       </c>
-      <c r="G38" s="28" t="n">
+      <c r="G47" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="H38" s="28" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Comms + financials lift</t>
         </is>
       </c>
-      <c r="I38" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K38" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L38" s="28" t="inlineStr">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>Iran exports surge &gt;40M bbls; Brent $71.57</t>
         </is>
       </c>
-      <c r="M38" s="28" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Dow 2nd straight record; Q3 begins</t>
         </is>
       </c>
-      <c r="N38" s="28" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>S&amp;P level derived</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="28" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Jul 2 2026</t>
         </is>
       </c>
-      <c r="B39" s="28" t="n">
+      <c r="B48" t="n">
         <v>7453.96</v>
       </c>
-      <c r="C39" s="28" t="n">
+      <c r="C48" t="n">
         <v>-0.0039</v>
       </c>
-      <c r="D39" s="28" t="n"/>
-      <c r="E39" s="28" t="n">
+      <c r="E48" t="n">
         <v>-0.0118</v>
       </c>
-      <c r="F39" s="28" t="n"/>
-      <c r="G39" s="28" t="n">
+      <c r="G48" t="n">
         <v>68</v>
       </c>
-      <c r="H39" s="28" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Nasdaq -1.18%</t>
         </is>
       </c>
-      <c r="I39" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K39" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L39" s="28" t="inlineStr">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>Crude below $68 (lowest since late Feb); Brent -21% in June</t>
         </is>
       </c>
-      <c r="M39" s="28" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>June jobs 57k vs 113k; unemployment 4.2%</t>
         </is>
       </c>
-      <c r="N39" s="28" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Dow +0.62%; weak jobs may cool Fed hawks</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>Jul 3 2026</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C49" s="41" t="n"/>
+      <c r="D49" s="41" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="n"/>
+      <c r="F49" s="41" t="n"/>
+      <c r="G49" s="41" t="n"/>
+      <c r="H49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="41" t="inlineStr">
+        <is>
+          <t>Independence Day (observed)</t>
+        </is>
+      </c>
+      <c r="N49" s="41" t="inlineStr">
+        <is>
+          <t>Markets closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>Jul 6 2026</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="n">
+        <v>7537.43</v>
+      </c>
+      <c r="C50" s="41" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="D50" s="41" t="n">
+        <v>26121.16</v>
+      </c>
+      <c r="E50" s="41" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="F50" s="41" t="n"/>
+      <c r="G50" s="41" t="n"/>
+      <c r="H50" s="41" t="inlineStr">
+        <is>
+          <t>AI optimism revives</t>
+        </is>
+      </c>
+      <c r="I50" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K50" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L50" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="41" t="inlineStr">
+        <is>
+          <t>Dow &gt;53,000; new closing record</t>
+        </is>
+      </c>
+      <c r="N50" s="41" t="inlineStr">
+        <is>
+          <t>TheStreet/Yahoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>Jul 7 2026</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="n">
+        <v>7503.85</v>
+      </c>
+      <c r="C51" s="41" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="D51" s="41" t="n">
+        <v>25818.69</v>
+      </c>
+      <c r="E51" s="41" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="F51" s="41" t="n"/>
+      <c r="G51" s="41" t="n"/>
+      <c r="H51" s="41" t="inlineStr">
+        <is>
+          <t>Tech gives back</t>
+        </is>
+      </c>
+      <c r="I51" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K51" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="41" t="inlineStr">
+        <is>
+          <t>Consolidation</t>
+        </is>
+      </c>
+      <c r="N51" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>Jul 8 2026</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="n">
+        <v>7482.71</v>
+      </c>
+      <c r="C52" s="41" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="D52" s="41" t="n"/>
+      <c r="E52" s="41" t="n"/>
+      <c r="F52" s="41" t="n">
+        <v>73.52</v>
+      </c>
+      <c r="G52" s="41" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="H52" s="41" t="inlineStr">
+        <is>
+          <t>Risk-off</t>
+        </is>
+      </c>
+      <c r="I52" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K52" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L52" s="41" t="inlineStr">
+        <is>
+          <t>WTI +4.4%, Brent +5.2%</t>
+        </is>
+      </c>
+      <c r="M52" s="41" t="inlineStr">
+        <is>
+          <t>Trump declares Iran ceasefire OVER; oil surges</t>
+        </is>
+      </c>
+      <c r="N52" s="41" t="inlineStr">
+        <is>
+          <t>WaPo/CNBC/Axios</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>Jul 9 2026</t>
+        </is>
+      </c>
+      <c r="B53" s="41" t="n">
+        <v>7543.64</v>
+      </c>
+      <c r="C53" s="41" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="D53" s="41" t="n"/>
+      <c r="E53" s="41" t="n"/>
+      <c r="F53" s="41" t="n"/>
+      <c r="G53" s="41" t="n"/>
+      <c r="H53" s="41" t="inlineStr">
+        <is>
+          <t>Semis jump</t>
+        </is>
+      </c>
+      <c r="I53" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J53" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K53" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L53" s="41" t="inlineStr">
+        <is>
+          <t>Oil eases after spike</t>
+        </is>
+      </c>
+      <c r="M53" s="41" t="inlineStr">
+        <is>
+          <t>Chips lead rebound</t>
+        </is>
+      </c>
+      <c r="N53" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>Jul 10 2026</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="n">
+        <v>7575.39</v>
+      </c>
+      <c r="C54" s="41" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="D54" s="41" t="n">
+        <v>26281.61</v>
+      </c>
+      <c r="E54" s="41" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="F54" s="41" t="n"/>
+      <c r="G54" s="41" t="n"/>
+      <c r="H54" s="41" t="inlineStr">
+        <is>
+          <t>Tech-led winning week</t>
+        </is>
+      </c>
+      <c r="I54" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J54" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K54" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L54" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M54" s="41" t="inlineStr">
+        <is>
+          <t>&gt;1% weekly S&amp;P advance</t>
+        </is>
+      </c>
+      <c r="N54" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>Jul 13 2026</t>
+        </is>
+      </c>
+      <c r="B55" s="41" t="n">
+        <v>7515.03</v>
+      </c>
+      <c r="C55" s="41" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="D55" s="41" t="n"/>
+      <c r="E55" s="41" t="n"/>
+      <c r="F55" s="41" t="n"/>
+      <c r="G55" s="41" t="n"/>
+      <c r="H55" s="41" t="inlineStr">
+        <is>
+          <t>Drift lower</t>
+        </is>
+      </c>
+      <c r="I55" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K55" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L55" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="41" t="inlineStr">
+        <is>
+          <t>Pre-earnings caution</t>
+        </is>
+      </c>
+      <c r="N55" s="41" t="inlineStr">
+        <is>
+          <t>Derived from Jul 14 +0.38% print</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>Jul 14 2026</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="n">
+        <v>7543.59</v>
+      </c>
+      <c r="C56" s="41" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="D56" s="41" t="n">
+        <v>26107.01</v>
+      </c>
+      <c r="E56" s="41" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F56" s="41" t="n"/>
+      <c r="G56" s="41" t="n"/>
+      <c r="H56" s="41" t="inlineStr">
+        <is>
+          <t>Nasdaq +0.9%</t>
+        </is>
+      </c>
+      <c r="I56" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K56" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L56" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="41" t="inlineStr">
+        <is>
+          <t>Rebound day</t>
+        </is>
+      </c>
+      <c r="N56" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>Jul 15 2026</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="n">
+        <v>7533.77</v>
+      </c>
+      <c r="C57" s="41" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="D57" s="41" t="n">
+        <v>25881.95</v>
+      </c>
+      <c r="E57" s="41" t="n">
+        <v>-0.0147</v>
+      </c>
+      <c r="F57" s="41" t="n"/>
+      <c r="G57" s="41" t="n"/>
+      <c r="H57" s="41" t="inlineStr">
+        <is>
+          <t>Alphabet &amp; chips sell off; SpaceX below IPO price</t>
+        </is>
+      </c>
+      <c r="I57" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K57" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L57" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" s="41" t="inlineStr">
+        <is>
+          <t>Chip slide begins</t>
+        </is>
+      </c>
+      <c r="N57" s="41" t="inlineStr">
+        <is>
+          <t>CNBC/TheStreet</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>Jul 16 2026</t>
+        </is>
+      </c>
+      <c r="B58" s="41" t="n"/>
+      <c r="C58" s="41" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="D58" s="41" t="n"/>
+      <c r="E58" s="41" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F58" s="41" t="n"/>
+      <c r="G58" s="41" t="n"/>
+      <c r="H58" s="41" t="inlineStr">
+        <is>
+          <t>Semiconductor slide continues</t>
+        </is>
+      </c>
+      <c r="I58" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K58" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L58" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M58" s="41" t="inlineStr">
+        <is>
+          <t>Dow +0.14% (defensive)</t>
+        </is>
+      </c>
+      <c r="N58" s="41" t="inlineStr">
+        <is>
+          <t>% confirmed; exact close n/d</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>Jul 17 2026</t>
+        </is>
+      </c>
+      <c r="B59" s="41" t="n">
+        <v>7457</v>
+      </c>
+      <c r="C59" s="41" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="D59" s="41" t="n">
+        <v>25520</v>
+      </c>
+      <c r="E59" s="41" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="F59" s="41" t="n"/>
+      <c r="G59" s="41" t="n"/>
+      <c r="H59" s="41" t="inlineStr">
+        <is>
+          <t>MOONSHOT AI SHOCK: Chinese startup rivals US models; global tech rout</t>
+        </is>
+      </c>
+      <c r="I59" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K59" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="41" t="inlineStr">
+        <is>
+          <t>Energy rises as oil spikes</t>
+        </is>
+      </c>
+      <c r="M59" s="41" t="inlineStr">
+        <is>
+          <t>Nasdaq week −2.90%; Dow 52,146; Iran re-escalation</t>
+        </is>
+      </c>
+      <c r="N59" s="41" t="inlineStr">
+        <is>
+          <t>TheStreet/Fool/WaPo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>Jul 20 2026</t>
+        </is>
+      </c>
+      <c r="B60" s="41" t="n"/>
+      <c r="C60" s="41" t="n"/>
+      <c r="D60" s="41" t="n"/>
+      <c r="E60" s="41" t="n"/>
+      <c r="F60" s="41" t="n"/>
+      <c r="G60" s="41" t="n">
+        <v>90</v>
+      </c>
+      <c r="H60" s="41" t="inlineStr">
+        <is>
+          <t>Modest chip comeback fails; Iran worries derail</t>
+        </is>
+      </c>
+      <c r="I60" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K60" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L60" s="41" t="inlineStr">
+        <is>
+          <t>Brent crosses above $90 — +30% off July lows</t>
+        </is>
+      </c>
+      <c r="M60" s="41" t="inlineStr">
+        <is>
+          <t>Iran intercepts 4 Hormuz vessels; US resumes blockade</t>
+        </is>
+      </c>
+      <c r="N60" s="41" t="inlineStr">
+        <is>
+          <t>CNBC/TheStreet</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>Jul 21 2026</t>
+        </is>
+      </c>
+      <c r="B61" s="41" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C61" s="41" t="n"/>
+      <c r="D61" s="41" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E61" s="41" t="n"/>
+      <c r="F61" s="41" t="n"/>
+      <c r="G61" s="41" t="n"/>
+      <c r="H61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="41" t="inlineStr">
+        <is>
+          <t>Session in progress at report time</t>
+        </is>
+      </c>
+      <c r="N61" s="41" t="inlineStr">
+        <is>
+          <t>Today — to be logged next cycle</t>
         </is>
       </c>
     </row>
@@ -2529,34 +3752,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7421875" defaultRowHeight="15"/>
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.609375" defaultRowHeight="15"/>
   <cols>
-    <col width="9.01171875" customWidth="1" min="1" max="1"/>
-    <col width="11.02734375" customWidth="1" min="2" max="2"/>
-    <col width="9.953125" customWidth="1" min="3" max="4"/>
-    <col width="11.02734375" customWidth="1" min="5" max="6"/>
-    <col width="9.953125" customWidth="1" min="7" max="7"/>
-    <col width="9.01171875" customWidth="1" min="8" max="8"/>
-    <col width="32.015625" customWidth="1" min="9" max="9"/>
-    <col width="37.93359375" customWidth="1" min="10" max="10"/>
+    <col width="9.01171875" customWidth="1" style="37" min="1" max="1"/>
+    <col width="11.02734375" customWidth="1" style="37" min="2" max="2"/>
+    <col width="9.953125" customWidth="1" style="37" min="3" max="4"/>
+    <col width="11.02734375" customWidth="1" style="37" min="5" max="6"/>
+    <col width="9.953125" customWidth="1" style="37" min="7" max="7"/>
+    <col width="9.01171875" customWidth="1" style="37" min="8" max="8"/>
+    <col width="32.015625" customWidth="1" style="37" min="9" max="9"/>
+    <col width="37.93359375" customWidth="1" style="37" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="37">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>S&amp;P 500 PRICE TRACKER — APRIL–MAY 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>Rolling daily closes | Moving averages | Momentum signals</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="30" customHeight="1" s="37">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Date</t>
@@ -2608,1061 +3831,1694 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24.75" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="24.75" customHeight="1" s="37">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Apr 20</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="5" t="n">
         <v>7109.14</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="5">
         <f>AVERAGE(B5:B5)</f>
         <v/>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="5">
         <f>AVERAGE(B5:B5)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="6">
         <f>(B5-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Nasdaq streak ended; mild pullback</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24.75" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="24.75" customHeight="1" s="37">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Apr 21</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="5" t="n">
         <v>7064.01</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="5">
         <f>B6-B5</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="6">
         <f>(B6-B5)/B5</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="5">
         <f>AVERAGE(B5:B6)</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="5">
         <f>AVERAGE(B5:B6)</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="6">
         <f>(B6-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Geopolitical wobble; Iran ceasefire watch</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="24.75" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="24.75" customHeight="1" s="37">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Apr 22</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="5" t="n">
         <v>7137.9</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="5">
         <f>B7-B6</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="6">
         <f>(B7-B6)/B6</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="5">
         <f>AVERAGE(B5:B7)</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="5">
         <f>AVERAGE(B5:B7)</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="6">
         <f>(B7-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Recovery; Nasdaq new ATH intraday</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24.75" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8" ht="24.75" customHeight="1" s="37">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Apr 23</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="5" t="n">
         <v>7108.4</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="5">
         <f>B8-B7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="6">
         <f>(B8-B7)/B7</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="5">
         <f>AVERAGE(B5:B8)</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="5">
         <f>AVERAGE(B5:B8)</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="6">
         <f>(B8-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Consolidation; profit-taking</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24.75" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="24.75" customHeight="1" s="37">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Apr 24</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="5" t="n">
         <v>7165.08</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="5">
         <f>B9-B8</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="6">
         <f>(B9-B8)/B8</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="5">
         <f>AVERAGE(B5:B9)</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="5">
         <f>AVERAGE(B5:B9)</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="6">
         <f>(B9-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Record close; chip/AI strength</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24.75" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+    <row r="10" ht="24.75" customHeight="1" s="37">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Apr 27</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="10" t="n">
         <v>7138.8</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="10">
         <f>B10-B9</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="11">
         <f>(B10-B9)/B9</f>
         <v/>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="10">
         <f>AVERAGE(B6:B10)</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="10">
         <f>AVERAGE(B5:B10)</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="11">
         <f>(B10-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>OpenAI growth concerns; oil pressure</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24.75" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="24.75" customHeight="1" s="37">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Apr 28</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="10" t="n">
         <v>7173.91</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="10">
         <f>B11-B10</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="11">
         <f>(B11-B10)/B10</f>
         <v/>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="10">
         <f>AVERAGE(B7:B11)</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="10">
         <f>AVERAGE(B5:B11)</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="11">
         <f>(B11-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>Fresh ATH 7,173.91 pre-Mag7</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24.75" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="12" ht="24.75" customHeight="1" s="37">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Apr 29</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="10" t="n">
         <v>7135.95</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="10">
         <f>B12-B11</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="11">
         <f>(B12-B11)/B11</f>
         <v/>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="10">
         <f>AVERAGE(B8:B12)</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="10">
         <f>AVERAGE(B6:B12)</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="11">
         <f>(B12-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>Fed pause; 10Y to 4.41%; Dow -280pts</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24.75" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="13" ht="24.75" customHeight="1" s="37">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Apr 30</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="10" t="n">
         <v>7155</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="10">
         <f>B13-B12</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="11">
         <f>(B13-B12)/B12</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="10">
         <f>AVERAGE(B9:B13)</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="10">
         <f>AVERAGE(B7:B13)</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="11">
         <f>(B13-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J13" s="19" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>Apple report; April MTD ~+10%</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="24.75" customHeight="1" s="37">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>May 1</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="10" t="n">
         <v>7230.12</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="10">
         <f>B14-B13</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="11">
         <f>(B14-B13)/B13</f>
         <v/>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="10">
         <f>AVERAGE(B10:B14)</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="10">
         <f>AVERAGE(B8:B14)</f>
         <v/>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="11">
         <f>(B14-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J14" s="19" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>ATH 7,230.12; best month since 2020</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24.75" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="15" ht="24.75" customHeight="1" s="37">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>May 4</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="10" t="n">
         <v>7200.75</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="10">
         <f>B15-B14</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="11">
         <f>(B15-B14)/B14</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="10">
         <f>AVERAGE(B11:B15)</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="10">
         <f>AVERAGE(B9:B15)</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="11">
         <f>(B15-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="I15" s="19" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J15" s="19" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>Risk-off; UAE missile intercept</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="16" ht="24.75" customHeight="1" s="37">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>May 5</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="10" t="n">
         <v>7259.22</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="10">
         <f>B16-B15</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="11">
         <f>(B16-B15)/B15</f>
         <v/>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="10">
         <f>AVERAGE(B12:B16)</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="10">
         <f>AVERAGE(B10:B16)</f>
         <v/>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="11">
         <f>(B16-6528.52)/6528.52</f>
         <v/>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>April +9.8%; May ATH path; oil-driven volatility</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>ATH 7,259.22; oil -10%; Russell 2k ATH</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>May 6</t>
         </is>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="18" t="n">
         <v>7365.12</v>
       </c>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n">
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n">
         <v>0.0146</v>
       </c>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="27" t="inlineStr">
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>US-Iran deal hopes</t>
         </is>
       </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="J17" s="18" t="inlineStr">
         <is>
           <t>S&amp;P +1.46%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>May 11</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="18" t="n">
         <v>7412</v>
       </c>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="inlineStr">
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="J18" s="18" t="inlineStr">
         <is>
           <t>New all-time high ~7,412</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>May 14</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="18" t="n">
         <v>7501.39</v>
       </c>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I19" s="27" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>First &gt;7,500</t>
         </is>
       </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="J19" s="18" t="inlineStr">
         <is>
           <t>Record 7,501.39</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>May 28</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="18" t="n">
         <v>7599.96</v>
       </c>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n">
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n">
         <v>0.0026</v>
       </c>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="inlineStr">
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>Approaching 7,600</t>
         </is>
       </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>Record 7,599.96</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Jun 2</t>
         </is>
       </c>
-      <c r="B21" s="27" t="n">
+      <c r="B21" s="18" t="n">
         <v>7609.78</v>
       </c>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n">
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n">
         <v>0.0013</v>
       </c>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
-      <c r="H21" s="27" t="inlineStr">
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I21" s="27" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>Goldman 7,600 met</t>
         </is>
       </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="J21" s="18" t="inlineStr">
         <is>
           <t>Record 7,609.78</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>Jun 4</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="n">
+        <v>7583.95</v>
+      </c>
+      <c r="C22" s="41" t="n"/>
+      <c r="D22" s="41" t="n"/>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="41" t="n"/>
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I22" s="41" t="inlineStr">
+        <is>
+          <t>Eve of rout</t>
+        </is>
+      </c>
+      <c r="J22" s="41" t="inlineStr">
+        <is>
+          <t>Derived from Jun 5 −2.64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Jun 5</t>
         </is>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B23" s="19" t="n">
         <v>7383.74</v>
       </c>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n">
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n">
         <v>-0.0264</v>
       </c>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="I22" s="28" t="inlineStr">
+      <c r="I23" s="19" t="inlineStr">
         <is>
           <t>Post-record chip rout</t>
         </is>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="J23" s="19" t="inlineStr">
         <is>
           <t>SOX -10.3%</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>Jun 8</t>
+        </is>
+      </c>
+      <c r="B24" s="41" t="n">
+        <v>7405.73</v>
+      </c>
+      <c r="C24" s="41" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="D24" s="41" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E24" s="41" t="n"/>
+      <c r="F24" s="41" t="n"/>
+      <c r="G24" s="41" t="n"/>
+      <c r="H24" s="41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I24" s="41" t="inlineStr">
+        <is>
+          <t>Post-rout stabilization</t>
+        </is>
+      </c>
+      <c r="J24" s="41" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>Jun 9</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="n">
+        <v>7386.65</v>
+      </c>
+      <c r="C25" s="41" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="E25" s="41" t="n"/>
+      <c r="F25" s="41" t="n"/>
+      <c r="G25" s="41" t="n"/>
+      <c r="H25" s="41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I25" s="41" t="inlineStr">
+        <is>
+          <t>Chip momentum fades</t>
+        </is>
+      </c>
+      <c r="J25" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>Jun 10</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="n">
+        <v>7266.99</v>
+      </c>
+      <c r="C26" s="41" t="n">
+        <v>-119.66</v>
+      </c>
+      <c r="D26" s="41" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="E26" s="41" t="n"/>
+      <c r="F26" s="41" t="n"/>
+      <c r="G26" s="41" t="n"/>
+      <c r="H26" s="41" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="I26" s="41" t="inlineStr">
+        <is>
+          <t>Pullback low</t>
+        </is>
+      </c>
+      <c r="J26" s="41" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="n">
+        <v>7394.3</v>
+      </c>
+      <c r="C27" s="41" t="n">
+        <v>127.31</v>
+      </c>
+      <c r="D27" s="41" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="E27" s="41" t="n"/>
+      <c r="F27" s="41" t="n"/>
+      <c r="G27" s="41" t="n"/>
+      <c r="H27" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I27" s="41" t="inlineStr">
+        <is>
+          <t>Sharp rebound</t>
+        </is>
+      </c>
+      <c r="J27" s="41" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Jun 12</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="n">
+        <v>7431.46</v>
+      </c>
+      <c r="C28" s="41" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="D28" s="41" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E28" s="41" t="n"/>
+      <c r="F28" s="41" t="n"/>
+      <c r="G28" s="41" t="n"/>
+      <c r="H28" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I28" s="41" t="inlineStr">
+        <is>
+          <t>Recovery extends</t>
+        </is>
+      </c>
+      <c r="J28" s="41" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Jun 15</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="n">
+        <v>7554.29</v>
+      </c>
+      <c r="C29" s="41" t="n">
+        <v>122.83</v>
+      </c>
+      <c r="D29" s="41" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="E29" s="41" t="n"/>
+      <c r="F29" s="41" t="n"/>
+      <c r="G29" s="41" t="n"/>
+      <c r="H29" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I29" s="41" t="inlineStr">
+        <is>
+          <t>War-end agreement; best day since April</t>
+        </is>
+      </c>
+      <c r="J29" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>Jun 16</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="n">
+        <v>7510.98</v>
+      </c>
+      <c r="C30" s="41" t="n">
+        <v>-43.31</v>
+      </c>
+      <c r="D30" s="41" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="41" t="n"/>
+      <c r="G30" s="41" t="n"/>
+      <c r="H30" s="41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I30" s="41" t="inlineStr">
+        <is>
+          <t>Warsh jitters; Dow −500</t>
+        </is>
+      </c>
+      <c r="J30" s="41" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Jun 17</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B31" s="19" t="n">
         <v>7420.1</v>
       </c>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="28" t="n">
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n">
         <v>-0.0121</v>
       </c>
-      <c r="E23" s="28" t="n"/>
-      <c r="F23" s="28" t="n"/>
-      <c r="G23" s="28" t="n"/>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="I23" s="28" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>Fed regime change</t>
         </is>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J31" s="19" t="inlineStr">
         <is>
           <t>Warsh; 9/18 hike</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Jun 18</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B32" s="19" t="n">
         <v>7500.58</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C32" s="19" t="n">
         <v>80.48</v>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D32" s="19" t="n">
         <v>0.0108</v>
       </c>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="19" t="n"/>
+      <c r="H32" s="19" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I24" s="28" t="inlineStr">
+      <c r="I32" s="19" t="inlineStr">
         <is>
           <t>Recovery</t>
         </is>
       </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="J32" s="19" t="inlineStr">
         <is>
           <t>Chips comeback</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B33" t="n">
         <v>7509</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C33" t="n">
         <v>8.42</v>
       </c>
-      <c r="D25" s="28" t="n">
+      <c r="D33" t="n">
         <v>0.0012</v>
       </c>
-      <c r="E25" s="28" t="n"/>
-      <c r="F25" s="28" t="n"/>
-      <c r="G25" s="28" t="n"/>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I25" s="28" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Consolidation</t>
         </is>
       </c>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Rebalance</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B34" t="n">
         <v>7365.46</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C34" t="n">
         <v>-143.54</v>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D34" t="n">
         <v>-0.0144</v>
       </c>
-      <c r="E26" s="28" t="n"/>
-      <c r="F26" s="28" t="n"/>
-      <c r="G26" s="28" t="n"/>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="I26" s="28" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>BofA 3-hike shock</t>
         </is>
       </c>
-      <c r="J26" s="28" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>SMH -6.5%</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B35" t="n">
         <v>7358.22</v>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C35" t="n">
         <v>-7.24</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D35" t="n">
         <v>-0.001</v>
       </c>
-      <c r="E27" s="28" t="n"/>
-      <c r="F27" s="28" t="n"/>
-      <c r="G27" s="28" t="n"/>
-      <c r="H27" s="28" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I27" s="28" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Rotation</t>
         </is>
       </c>
-      <c r="J27" s="28" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Pre-Micron</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B36" t="n">
         <v>7357.49</v>
       </c>
-      <c r="C28" s="28" t="n">
+      <c r="C36" t="n">
         <v>-0.73</v>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D36" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="E28" s="28" t="n"/>
-      <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I28" s="28" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Flat</t>
         </is>
       </c>
-      <c r="J28" s="28" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Tech drag</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="B29" s="28" t="n">
+      <c r="B37" t="n">
         <v>7445</v>
       </c>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n">
+      <c r="D37" t="n">
         <v>0.012</v>
       </c>
-      <c r="E29" s="28" t="n"/>
-      <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="n"/>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I29" s="28" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Dow &gt;52k</t>
         </is>
       </c>
-      <c r="J29" s="28" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Derived +1.2%</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B30" s="28" t="n">
+      <c r="B38" t="n">
         <v>7449.36</v>
       </c>
-      <c r="C30" s="28" t="n">
+      <c r="C38" t="n">
         <v>4.36</v>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D38" t="n">
         <v>0.0003</v>
       </c>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="28" t="n"/>
-      <c r="G30" s="28" t="n"/>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I30" s="28" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Best quarter since 2020</t>
         </is>
       </c>
-      <c r="J30" s="28" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Q2 close</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B31" s="28" t="n">
+      <c r="B39" t="n">
         <v>7483</v>
       </c>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="28" t="n">
+      <c r="D39" t="n">
         <v>0.0045</v>
       </c>
-      <c r="E31" s="28" t="n"/>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="28" t="n"/>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Q3; Dow record</t>
         </is>
       </c>
-      <c r="J31" s="28" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Derived</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n">
+      <c r="B40" t="n">
         <v>7453.96</v>
       </c>
-      <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n">
+      <c r="D40" t="n">
         <v>-0.0039</v>
       </c>
-      <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Weak jobs 57k</t>
         </is>
       </c>
-      <c r="J32" s="28" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Unemp 4.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>Jul 6</t>
+        </is>
+      </c>
+      <c r="B41" s="41" t="n">
+        <v>7537.43</v>
+      </c>
+      <c r="C41" s="41" t="n"/>
+      <c r="D41" s="41" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="E41" s="41" t="n"/>
+      <c r="F41" s="41" t="n"/>
+      <c r="G41" s="41" t="n"/>
+      <c r="H41" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I41" s="41" t="inlineStr">
+        <is>
+          <t>Dow &gt;53k record</t>
+        </is>
+      </c>
+      <c r="J41" s="41" t="inlineStr">
+        <is>
+          <t>TheStreet</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>Jul 7</t>
+        </is>
+      </c>
+      <c r="B42" s="41" t="n">
+        <v>7503.85</v>
+      </c>
+      <c r="C42" s="41" t="n">
+        <v>-33.58</v>
+      </c>
+      <c r="D42" s="41" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="E42" s="41" t="n"/>
+      <c r="F42" s="41" t="n"/>
+      <c r="G42" s="41" t="n"/>
+      <c r="H42" s="41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I42" s="41" t="inlineStr">
+        <is>
+          <t>Consolidation</t>
+        </is>
+      </c>
+      <c r="J42" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>Jul 8</t>
+        </is>
+      </c>
+      <c r="B43" s="41" t="n">
+        <v>7482.71</v>
+      </c>
+      <c r="C43" s="41" t="n">
+        <v>-21.14</v>
+      </c>
+      <c r="D43" s="41" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="E43" s="41" t="n"/>
+      <c r="F43" s="41" t="n"/>
+      <c r="G43" s="41" t="n"/>
+      <c r="H43" s="41" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="I43" s="41" t="inlineStr">
+        <is>
+          <t>Ceasefire declared over</t>
+        </is>
+      </c>
+      <c r="J43" s="41" t="inlineStr">
+        <is>
+          <t>WaPo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>Jul 9</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="n">
+        <v>7543.64</v>
+      </c>
+      <c r="C44" s="41" t="n">
+        <v>60.93</v>
+      </c>
+      <c r="D44" s="41" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="E44" s="41" t="n"/>
+      <c r="F44" s="41" t="n"/>
+      <c r="G44" s="41" t="n"/>
+      <c r="H44" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I44" s="41" t="inlineStr">
+        <is>
+          <t>Semis jump; oil eases</t>
+        </is>
+      </c>
+      <c r="J44" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>Jul 10</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="n">
+        <v>7575.39</v>
+      </c>
+      <c r="C45" s="41" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="D45" s="41" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="E45" s="41" t="n"/>
+      <c r="F45" s="41" t="n"/>
+      <c r="G45" s="41" t="n"/>
+      <c r="H45" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I45" s="41" t="inlineStr">
+        <is>
+          <t>Winning week</t>
+        </is>
+      </c>
+      <c r="J45" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>Jul 13</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="n">
+        <v>7515.03</v>
+      </c>
+      <c r="C46" s="41" t="n">
+        <v>-60.36</v>
+      </c>
+      <c r="D46" s="41" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="E46" s="41" t="n"/>
+      <c r="F46" s="41" t="n"/>
+      <c r="G46" s="41" t="n"/>
+      <c r="H46" s="41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I46" s="41" t="inlineStr">
+        <is>
+          <t>Derived from Jul 14 print</t>
+        </is>
+      </c>
+      <c r="J46" s="41" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>Jul 14</t>
+        </is>
+      </c>
+      <c r="B47" s="41" t="n">
+        <v>7543.59</v>
+      </c>
+      <c r="C47" s="41" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="D47" s="41" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="E47" s="41" t="n"/>
+      <c r="F47" s="41" t="n"/>
+      <c r="G47" s="41" t="n"/>
+      <c r="H47" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I47" s="41" t="inlineStr">
+        <is>
+          <t>Rebound</t>
+        </is>
+      </c>
+      <c r="J47" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>Jul 15</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="n">
+        <v>7533.77</v>
+      </c>
+      <c r="C48" s="41" t="n">
+        <v>-9.82</v>
+      </c>
+      <c r="D48" s="41" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="E48" s="41" t="n"/>
+      <c r="F48" s="41" t="n"/>
+      <c r="G48" s="41" t="n"/>
+      <c r="H48" s="41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I48" s="41" t="inlineStr">
+        <is>
+          <t>Alphabet/chip selloff</t>
+        </is>
+      </c>
+      <c r="J48" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>Jul 16</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="n"/>
+      <c r="C49" s="41" t="n"/>
+      <c r="D49" s="41" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="E49" s="41" t="n"/>
+      <c r="F49" s="41" t="n"/>
+      <c r="G49" s="41" t="n"/>
+      <c r="H49" s="41" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="I49" s="41" t="inlineStr">
+        <is>
+          <t>Semis slide; close n/d</t>
+        </is>
+      </c>
+      <c r="J49" s="41" t="inlineStr">
+        <is>
+          <t>TheStreet</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>Jul 17</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="n">
+        <v>7457</v>
+      </c>
+      <c r="C50" s="41" t="n"/>
+      <c r="D50" s="41" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="E50" s="41" t="n"/>
+      <c r="F50" s="41" t="n"/>
+      <c r="G50" s="41" t="n"/>
+      <c r="H50" s="41" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="I50" s="41" t="inlineStr">
+        <is>
+          <t>Moonshot AI shock; Iran</t>
+        </is>
+      </c>
+      <c r="J50" s="41" t="inlineStr">
+        <is>
+          <t>TheStreet</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="n"/>
+      <c r="C51" s="41" t="n"/>
+      <c r="D51" s="41" t="n"/>
+      <c r="E51" s="41" t="n"/>
+      <c r="F51" s="41" t="n"/>
+      <c r="G51" s="41" t="n"/>
+      <c r="H51" s="41" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="I51" s="41" t="inlineStr">
+        <is>
+          <t>Slightly lower; Brent &gt;$90</t>
+        </is>
+      </c>
+      <c r="J51" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>Jul 21</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C52" s="41" t="n"/>
+      <c r="D52" s="41" t="n"/>
+      <c r="E52" s="41" t="n"/>
+      <c r="F52" s="41" t="n"/>
+      <c r="G52" s="41" t="n"/>
+      <c r="H52" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="41" t="inlineStr">
+        <is>
+          <t>Session in progress</t>
+        </is>
+      </c>
+      <c r="J52" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3682,32 +5538,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7421875" defaultRowHeight="15"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.609375" defaultRowHeight="15"/>
   <cols>
-    <col width="9.01171875" customWidth="1" min="1" max="1"/>
-    <col width="11.97265625" customWidth="1" min="2" max="3"/>
-    <col width="13.98828125" customWidth="1" min="4" max="4"/>
-    <col width="9.953125" customWidth="1" min="5" max="5"/>
-    <col width="11.02734375" customWidth="1" min="6" max="7"/>
-    <col width="37.93359375" customWidth="1" min="8" max="8"/>
+    <col width="9.01171875" customWidth="1" style="37" min="1" max="1"/>
+    <col width="11.97265625" customWidth="1" style="37" min="2" max="3"/>
+    <col width="13.98828125" customWidth="1" style="37" min="4" max="4"/>
+    <col width="9.953125" customWidth="1" style="37" min="5" max="5"/>
+    <col width="11.02734375" customWidth="1" style="37" min="6" max="7"/>
+    <col width="37.93359375" customWidth="1" style="37" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="37">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>CRUDE OIL PRICE TRACKER — WTI &amp; BRENT</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>Daily closes | Spread analysis | Geopolitical drivers</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="30" customHeight="1" s="37">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Date</t>
@@ -3750,29 +5606,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Apr 20</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="14" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="14" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="14">
         <f>C5-B5</f>
         <v/>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="6">
         <f>(C5-102)/102</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="6">
         <f>(C5-65.83)/65.83</f>
         <v/>
       </c>
@@ -3783,30 +5639,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Apr 22</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="14" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="14">
         <f>C6-B6</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="6">
         <f>(B6-B5)/B5</f>
         <v/>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="6">
         <f>(C6-102)/102</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="6">
         <f>(C6-65.83)/65.83</f>
         <v/>
       </c>
@@ -3817,30 +5673,30 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Apr 23</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="14" t="n">
         <v>95.5</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="14">
         <f>C7-B7</f>
         <v/>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="6">
         <f>(B7-B6)/B6</f>
         <v/>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="6">
         <f>(C7-102)/102</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="6">
         <f>(C7-65.83)/65.83</f>
         <v/>
       </c>
@@ -3851,30 +5707,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Apr 24</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="14" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="14" t="n">
         <v>105.33</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="14">
         <f>C8-B8</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="6">
         <f>(B8-B7)/B7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="6">
         <f>(C8-102)/102</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="6">
         <f>(C8-65.83)/65.83</f>
         <v/>
       </c>
@@ -3885,30 +5741,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="14" t="n">
         <v>94.04000000000001</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="14" t="n">
         <v>105.33</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="14">
         <f>C9-B9</f>
         <v/>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="6">
         <f>(B9-B8)/B8</f>
         <v/>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="6">
         <f>(C9-102)/102</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="6">
         <f>(C9-65.83)/65.83</f>
         <v/>
       </c>
@@ -3919,30 +5775,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="14" t="n">
         <v>93.68000000000001</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="14" t="n">
         <v>105.2</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="14">
         <f>C10-B10</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="6">
         <f>(B10-B9)/B9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="6">
         <f>(C10-102)/102</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="6">
         <f>(C10-65.83)/65.83</f>
         <v/>
       </c>
@@ -3953,444 +5809,526 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Apr 27</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n">
+      <c r="B11" s="15" t="n">
         <v>95.5</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="15">
         <f>C11-B11</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="11">
         <f>(B11-B10)/B10</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="11">
         <f>(C11-102)/102</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="11">
         <f>(C11-65.83)/65.83</f>
         <v/>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Hormuz risk back; supply concerns</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Apr 28</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="15" t="n">
         <v>96</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="15" t="n">
         <v>108</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="15">
         <f>C12-B12</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="11">
         <f>(B12-B11)/B11</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="11">
         <f>(C12-102)/102</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="11">
         <f>(C12-65.83)/65.83</f>
         <v/>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Ceasefire fragile but holding</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Apr 29</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="15" t="n">
         <v>96.5</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="15" t="n">
         <v>108.5</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="15">
         <f>C13-B13</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="11">
         <f>(B13-B12)/B12</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="11">
         <f>(C13-102)/102</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="11">
         <f>(C13-65.83)/65.83</f>
         <v/>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Supply-side firmness</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Apr 30</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="15" t="n">
         <v>95.8</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="15" t="n">
         <v>107.8</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="15">
         <f>C14-B14</f>
         <v/>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="11">
         <f>(B14-B13)/B13</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="11">
         <f>(C14-102)/102</f>
         <v/>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="11">
         <f>(C14-65.83)/65.83</f>
         <v/>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Diplomacy progress</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>May 1</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="15">
         <f>C15-B15</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="11">
         <f>(B15-B14)/B14</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="11">
         <f>(C15-102)/102</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="11">
         <f>(C15-65.83)/65.83</f>
         <v/>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>End of strong April</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="16" ht="24.75" customHeight="1" s="37">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>May 4</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n">
+      <c r="B16" s="15" t="n">
         <v>102.27</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="15" t="n">
         <v>109.87</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="15">
         <f>C16-B16</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="11">
         <f>(B16-B15)/B15</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="11">
         <f>(C16-102)/102</f>
         <v/>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="11">
         <f>(C16-65.83)/65.83</f>
         <v/>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>UAE missile intercept; Iran small boats engaged</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24.75" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="17" ht="24.75" customHeight="1" s="37">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>May 5</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n">
+      <c r="B17" s="15" t="n">
         <v>102.27</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="15" t="n">
         <v>109.87</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="15">
         <f>C17-B17</f>
         <v/>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="11">
         <f>(B17-B16)/B16</f>
         <v/>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="11">
         <f>(C17-102)/102</f>
         <v/>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="11">
         <f>(C17-65.83)/65.83</f>
         <v/>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>WTI -3.9%, Brent -3.99% on Hegseth ceasefire reaffirm</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>May 15</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n">
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n">
         <v>113</v>
       </c>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="inlineStr">
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>Brent peaks &gt;$113 on Hormuz disruption (2026 high)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Jun 5</t>
         </is>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="19" t="n">
         <v>93.45</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="19" t="n">
         <v>97.44</v>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D19" s="19" t="n">
         <v>3.99</v>
       </c>
-      <c r="E19" s="28" t="n"/>
-      <c r="F19" s="28" t="n"/>
-      <c r="G19" s="28" t="n"/>
-      <c r="H19" s="28" t="inlineStr">
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>Post-gap; premium fading</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Jun 20</t>
         </is>
       </c>
-      <c r="B20" s="28" t="n">
+      <c r="B20" s="19" t="n">
         <v>77.54000000000001</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="19" t="n">
         <v>80.56999999999999</v>
       </c>
-      <c r="D20" s="28" t="n">
+      <c r="D20" s="19" t="n">
         <v>3.03</v>
       </c>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="28" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="28" t="inlineStr">
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="inlineStr">
         <is>
           <t>Iran re-closed Hormuz; ceasefire tentative</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="19" t="n">
         <v>74.3</v>
       </c>
-      <c r="C21" s="28" t="n">
+      <c r="C21" s="19" t="n">
         <v>78.41</v>
       </c>
-      <c r="D21" s="28" t="n">
+      <c r="D21" s="19" t="n">
         <v>4.11</v>
       </c>
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="n"/>
-      <c r="H21" s="28" t="inlineStr">
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>VP Vance 'good foundation'</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="19" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="19" t="n">
         <v>78</v>
       </c>
-      <c r="D22" s="28" t="n">
+      <c r="D22" s="19" t="n">
         <v>4.6</v>
       </c>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>US 60-day Iran oil waiver; 67M bbls</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="19" t="n">
         <v>69.5</v>
       </c>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="28" t="n"/>
-      <c r="E23" s="28" t="n"/>
-      <c r="F23" s="28" t="n"/>
-      <c r="G23" s="28" t="n"/>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>WTI &lt;$70 after cargo-ship attack near Oman</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n"/>
-      <c r="C24" s="28" t="n">
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n">
         <v>73.17</v>
       </c>
-      <c r="D24" s="28" t="n"/>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>Renewed US-Iran strikes</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="19" t="n">
         <v>68.58</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="19" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="D25" s="28" t="n">
+      <c r="D25" s="19" t="n">
         <v>2.99</v>
       </c>
-      <c r="E25" s="28" t="n"/>
-      <c r="F25" s="28" t="n"/>
-      <c r="G25" s="28" t="n"/>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="inlineStr">
         <is>
           <t>Iran exports surge &gt;40M bbls; &gt;10M bpd via Hormuz</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="19" t="n">
         <v>68</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C26" s="19" t="n">
         <v>68</v>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="28" t="n"/>
-      <c r="F26" s="28" t="n"/>
-      <c r="G26" s="28" t="n"/>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>Crude &lt;$68 (lowest since late Feb); Brent -21% June</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>Jul 8</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="n">
+        <v>73.52</v>
+      </c>
+      <c r="C27" s="41" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="D27" s="41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E27" s="41" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="F27" s="41" t="n"/>
+      <c r="G27" s="41" t="n"/>
+      <c r="H27" s="41" t="inlineStr">
+        <is>
+          <t>Trump declares Iran ceasefire over; WTI +4.4%, Brent +5.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Jul 9</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="n"/>
+      <c r="C28" s="41" t="n"/>
+      <c r="D28" s="41" t="n"/>
+      <c r="E28" s="41" t="n"/>
+      <c r="F28" s="41" t="n"/>
+      <c r="G28" s="41" t="n"/>
+      <c r="H28" s="41" t="inlineStr">
+        <is>
+          <t>Prices ease after spike; supply-disruption fears persist</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Jul 17</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="n"/>
+      <c r="C29" s="41" t="n"/>
+      <c r="D29" s="41" t="n"/>
+      <c r="E29" s="41" t="n"/>
+      <c r="F29" s="41" t="n"/>
+      <c r="G29" s="41" t="n"/>
+      <c r="H29" s="41" t="inlineStr">
+        <is>
+          <t>Oil spikes; energy stocks rally as tech routs</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="n"/>
+      <c r="C30" s="41" t="n">
+        <v>90</v>
+      </c>
+      <c r="D30" s="41" t="n"/>
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="41" t="n"/>
+      <c r="G30" s="41" t="n"/>
+      <c r="H30" s="41" t="inlineStr">
+        <is>
+          <t>Brent crosses $90 (+30% off July lows); Iran intercepts 4 Hormuz vessels; US resumes blockade</t>
         </is>
       </c>
     </row>
@@ -4410,34 +6348,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7421875" defaultRowHeight="15"/>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.609375" defaultRowHeight="15"/>
   <cols>
-    <col width="9.01171875" customWidth="1" min="1" max="1"/>
-    <col width="11.97265625" customWidth="1" min="2" max="2"/>
-    <col width="13.98828125" customWidth="1" min="3" max="3"/>
-    <col width="50.04296875" customWidth="1" min="4" max="4"/>
-    <col width="22.05859375" customWidth="1" min="5" max="5"/>
-    <col width="13.98828125" customWidth="1" min="6" max="6"/>
-    <col width="27.98046875" customWidth="1" min="7" max="7"/>
-    <col width="11.02734375" customWidth="1" min="8" max="8"/>
+    <col width="9.01171875" customWidth="1" style="37" min="1" max="1"/>
+    <col width="11.97265625" customWidth="1" style="37" min="2" max="2"/>
+    <col width="13.98828125" customWidth="1" style="37" min="3" max="3"/>
+    <col width="50.04296875" customWidth="1" style="37" min="4" max="4"/>
+    <col width="22.05859375" customWidth="1" style="37" min="5" max="5"/>
+    <col width="13.98828125" customWidth="1" style="37" min="6" max="6"/>
+    <col width="27.98046875" customWidth="1" style="37" min="7" max="7"/>
+    <col width="11.02734375" customWidth="1" style="37" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="37">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>SECTOR INTELLIGENCE LOG — AI | M&amp;A/PE | HEALTHCARE | DEFENSE | OIL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>Key deals, signals, and developments by sector</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="30" customHeight="1" s="37">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Date</t>
@@ -4480,1134 +6418,1428 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Apr 27</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>PE Acquisition</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Apollo acquires Forvia auto interiors</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>$2.1B</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Cross-sector PE</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Apr 27</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Take-Private</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Blackstone consortium / Senior plc UK aerospace</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>£1.4B (~$1.9B)</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>UK aero/def consolidation</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Apr 27</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Generics M&amp;A</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Sun Pharma acquires Organon</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>$11.75B</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Pharma rollup</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Apr 28</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Earnings Setup</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Mag7 reports begin; hyperscaler capex ~$700B</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>AI capex super-cycle</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Apr 29</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Macro</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Fed Decision</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Fed split vote; H2 cut timing unresolved</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>10Y→4.41%</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Rate-sensitive headwind</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Apr 30</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Goldman raises S&amp;P target to 7,600</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>+12% EPS growth</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>AI capex tailwind</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>May 1</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Q1 Aggregate</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Q1 PE M&amp;A: 614 deals, $154.6B (+12.6% YoY)</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>22 deals &gt;$10B (record)</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Megadeal concentration</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>May 1</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>YTD share buyback authorizations record</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>$422B</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Capital return strength</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>May 4</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Geopolitical</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>UAE missile intercept; US engages Iran small boats</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>BEARISH (oil↑)</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Hormuz tension flare</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>May 5</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Semis</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Micron &gt;$700B mkt cap; HBM sold out 2026</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>+10% intraday</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>AI memory tightness</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>May 5</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Price Action</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>WTI -3.9% to $102.27; Brent -3.99% to $109.87</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Oil-equity inverse correl</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>BULLISH equity</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Hegseth ceasefire reaffirm</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16" ht="24.75" customHeight="1" s="37">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>May 5</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Big Tech</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Wiz/Alphabet $32B all-cash advancing</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>First major Big Tech deal under FTC Ferguson</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Regulatory test case</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>May 14</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>S&amp;P first close above 7,500</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>7,501.39</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>Forbes</t>
         </is>
       </c>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="H17" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>May 27</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>Micron joins $1T market-cap club</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>$1T</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>Fortune</t>
         </is>
       </c>
-      <c r="H18" s="28" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>May 29</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>PE / AI</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Private Credit</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Apollo &amp; Blackstone package funds Anthropic TPU deal</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>$36B</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>BULLISH / concentration</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>Mega PC into AI</t>
         </is>
       </c>
-      <c r="H19" s="28" t="inlineStr">
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Jun 2</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>S&amp;P record 7,609.78 (Goldman 7,600 target met early)</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>7,609.78</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>CNBC</t>
         </is>
       </c>
-      <c r="H20" s="28" t="inlineStr">
+      <c r="H20" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Jun 5</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Selloff</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Chip rout: SOX -10.3% on Broadcom soft guide</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>Air-pocket #1</t>
         </is>
       </c>
-      <c r="H21" s="28" t="inlineStr">
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Jun 17</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Macro</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Fed</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Regime change: Warsh; 9/18 project 2026 hike</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>3.50-3.75%</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>Fed.gov</t>
         </is>
       </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Jun 19</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>PE / Industrials</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Carve-out</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Montagu acquires BMC Helix</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>PE Hub</t>
         </is>
       </c>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Jun 19</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>PE / Energy</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Acq+JV</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>NextEra / Caliber Resource Partners + Quantum JV</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>$1.3B</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>Middle Market</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Macro</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>BofA: 3 Fed hikes 2026 (Sep/Oct/Dec)-&gt;4.25-4.50%</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>CNBC/Fortune</t>
         </is>
       </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="H25" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B26" s="28" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="C26" s="28" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Selloff</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>SMH -6.5%; KOSPI -9.99% (air-pocket #2)</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="G26" s="28" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>TheStreet</t>
         </is>
       </c>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B27" s="28" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Oil</t>
         </is>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>Geopolitical</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>US 60-day Iran oil sanctions waiver; 67M bbls unlocked</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>67M bbl</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>BEARISH (spot oil)</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>CNBC</t>
         </is>
       </c>
-      <c r="H27" s="28" t="inlineStr">
+      <c r="H27" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Oil</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>WTI &lt;$70 after cargo-ship attack near Oman</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>&lt;$70</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>CNBC</t>
         </is>
       </c>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="H28" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Oil</t>
         </is>
       </c>
-      <c r="C29" s="28" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Geopolitical</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Renewed US-Iran strikes reignite Hormuz fears</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>Brent $73.17</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>VOLATILE</t>
         </is>
       </c>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>CNBC</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>US indexes wrap best quarter since 2020</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
-      <c r="G30" s="28" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>TheStreet</t>
         </is>
       </c>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="H30" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>Macro</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>Jobs</t>
         </is>
       </c>
-      <c r="D31" s="28" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>June payrolls 57k vs 113k est; unemployment 4.2%</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>57k</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>BLS/Yahoo</t>
         </is>
       </c>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H31" s="19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>Jun 15</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="C32" s="41" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
+      <c r="D32" s="41" t="inlineStr">
+        <is>
+          <t>Trump announces agreement to end US-Iran war; S&amp;P +1.65% best day since April</t>
+        </is>
+      </c>
+      <c r="E32" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="41" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G32" s="41" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="H32" s="41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Take-Private</t>
+        </is>
+      </c>
+      <c r="D33" s="41" t="inlineStr">
+        <is>
+          <t>Castlelake agrees $7.3B takeover of easyJet (690p/share cash)</t>
+        </is>
+      </c>
+      <c r="E33" s="41" t="inlineStr">
+        <is>
+          <t>$7.3B</t>
+        </is>
+      </c>
+      <c r="F33" s="41" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G33" s="41" t="inlineStr">
+        <is>
+          <t>CBS/Markets Group</t>
+        </is>
+      </c>
+      <c r="H33" s="41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>Jul 8</t>
+        </is>
+      </c>
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
+      <c r="D34" s="41" t="inlineStr">
+        <is>
+          <t>Iran ceasefire declared OVER; WTI +4.4% to $73.52, Brent +5.2% to $78.02</t>
+        </is>
+      </c>
+      <c r="E34" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="41" t="inlineStr">
+        <is>
+          <t>BULLISH (oil) / BEARISH (equities)</t>
+        </is>
+      </c>
+      <c r="G34" s="41" t="inlineStr">
+        <is>
+          <t>WaPo/CNBC/Axios</t>
+        </is>
+      </c>
+      <c r="H34" s="41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Jul 15</t>
+        </is>
+      </c>
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>Private mkts</t>
+        </is>
+      </c>
+      <c r="D35" s="41" t="inlineStr">
+        <is>
+          <t>SpaceX trades below IPO price for first time</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="41" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G35" s="41" t="inlineStr">
+        <is>
+          <t>TheStreet</t>
+        </is>
+      </c>
+      <c r="H35" s="41" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Jul 17</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>Competitive shock</t>
+        </is>
+      </c>
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>Moonshot AI (China) releases model rivaling US frontier labs; global tech rout, Nasdaq wk −2.9%</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="41" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G36" s="41" t="inlineStr">
+        <is>
+          <t>Fool/TheStreet</t>
+        </is>
+      </c>
+      <c r="H36" s="41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>Jul 19</t>
+        </is>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>PE / M&amp;A</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D37" s="41" t="inlineStr">
+        <is>
+          <t>EA $55B LBO stalls at CFIUS (PIF national-security review); outside date pushed to Sep 28</t>
+        </is>
+      </c>
+      <c r="E37" s="41" t="inlineStr">
+        <is>
+          <t>$55B</t>
+        </is>
+      </c>
+      <c r="F37" s="41" t="inlineStr">
+        <is>
+          <t>BEARISH (deal risk)</t>
+        </is>
+      </c>
+      <c r="G37" s="41" t="inlineStr">
+        <is>
+          <t>Tech-Insider</t>
+        </is>
+      </c>
+      <c r="H37" s="41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Supply shock</t>
+        </is>
+      </c>
+      <c r="D38" s="41" t="inlineStr">
+        <is>
+          <t>Brent &gt;$90, +30% off July lows; Iran intercepts 4 vessels in Hormuz; US resumes port blockade</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>$90+</t>
+        </is>
+      </c>
+      <c r="F38" s="41" t="inlineStr">
+        <is>
+          <t>BULLISH (oil)</t>
+        </is>
+      </c>
+      <c r="G38" s="41" t="inlineStr">
+        <is>
+          <t>CNBC/TheStreet</t>
+        </is>
+      </c>
+      <c r="H38" s="41" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5629,179 +7861,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7421875" defaultRowHeight="15"/>
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.609375" defaultRowHeight="15"/>
   <cols>
-    <col width="89.99609375" customWidth="1" min="1" max="1"/>
+    <col width="89.99609375" customWidth="1" style="37" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="37">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>REFERENCE &amp; METHODOLOGY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="n"/>
+      <c r="A2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Data sources:</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>• S&amp;P 500 / Nasdaq closes: FRED St. Louis Fed (SP500, NASDAQCOM series)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>• WTI / Brent: TradingEconomics, Investing.com, Fortune oil reports, EIA</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>• Deal flow: Reuters, Bloomberg, PE Wire, CNBC, Cleary Gottlieb, HarbourVest</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n"/>
+      <c r="A7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Tracking conventions:</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>• Daily Δ% calculated against prior trading day (excludes weekends/holidays)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>• April MTD% benchmarked to Mar 31, 2026 close (6,528.52)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>• Brent-WTI spread = Brent − WTI; flag when &gt;$10 (geopolitical premium signal)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>• Yellow rows = newly added since last Drive update (Apr 27 → May 5, 2026)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n"/>
+      <c r="A13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Roadmap status (per original architecture):</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>• ✅ Master Log (live)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>• ✅ S&amp;P 500 Tracker with 5/7-day MA + MTD% (live)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>• ✅ Oil Tracker with WTI-Brent spread (live)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>• ✅ Sector Intelligence Log (live)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>• ⏳ PE Deal Register (next - dedicated structure)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>• ⏳ Macro Scorecard (next)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>• ⏳ Sector Momentum dashboard (next)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="n"/>
+      <c r="A22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Update protocol:</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>• On every 'Daily report' command, append a row to Master Log + S&amp;P Tracker + Oil Tracker</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>• Sector Intelligence Log updated when material deal/headline emerges</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>• Last Updated timestamp on Master Log A2 must be revised each touch</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -5834,6 +8065,63 @@
       <c r="A32" t="inlineStr">
         <is>
           <t>- This workbook is the canonical loop target; /daily-report appends here each cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Finalization update (2026-07-21):</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>- Coverage now continuous Apr 20 -&gt; Jul 21 2026 across all tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>- Jun 8-12, Jun 15, Jul 6-10, Jul 14-17 closes are sourced prints (FRED/CNBC/TheStreet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>- Derived closes (from confirmed % moves, flagged in Notes): Jun 4, Jun 16, Jul 13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>- Jul 16 &amp; Jul 20 exact S&amp;P closes not yet published in sources; % moves and drivers logged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>- May 7-13, May 15-26 non-milestone dailies: not published in available sources; milestone closes logged (May 11, 14, 27, 28, 29); May 25 Memorial Day closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>- Jul 21 marked PENDING (session in progress at report time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>- Blue-filled rows = added in the Jul 21 finalization pass.</t>
         </is>
       </c>
     </row>

--- a/MI_PE_Tracking_System.xlsx
+++ b/MI_PE_Tracking_System.xlsx
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -250,6 +250,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3846,13 +3854,11 @@
       <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
-        <f>AVERAGE(B5:B5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="5">
-        <f>AVERAGE(B5:B5)</f>
-        <v/>
+      <c r="E5" s="5" t="n">
+        <v>7109.14</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>7109.14</v>
       </c>
       <c r="G5" s="6">
         <f>(B5-6528.52)/6528.52</f>
@@ -3891,13 +3897,11 @@
         <f>(B6-B5)/B5</f>
         <v/>
       </c>
-      <c r="E6" s="5">
-        <f>AVERAGE(B5:B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="5">
-        <f>AVERAGE(B5:B6)</f>
-        <v/>
+      <c r="E6" s="5" t="n">
+        <v>7086.58</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7086.58</v>
       </c>
       <c r="G6" s="6">
         <f>(B6-6528.52)/6528.52</f>
@@ -3936,13 +3940,11 @@
         <f>(B7-B6)/B6</f>
         <v/>
       </c>
-      <c r="E7" s="5">
-        <f>AVERAGE(B5:B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="5">
-        <f>AVERAGE(B5:B7)</f>
-        <v/>
+      <c r="E7" s="5" t="n">
+        <v>7123.52</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7123.52</v>
       </c>
       <c r="G7" s="6">
         <f>(B7-6528.52)/6528.52</f>
@@ -3981,13 +3983,11 @@
         <f>(B8-B7)/B7</f>
         <v/>
       </c>
-      <c r="E8" s="5">
-        <f>AVERAGE(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="5">
-        <f>AVERAGE(B5:B8)</f>
-        <v/>
+      <c r="E8" s="5" t="n">
+        <v>7108.77</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>7108.77</v>
       </c>
       <c r="G8" s="6">
         <f>(B8-6528.52)/6528.52</f>
@@ -4026,13 +4026,11 @@
         <f>(B9-B8)/B8</f>
         <v/>
       </c>
-      <c r="E9" s="5">
-        <f>AVERAGE(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="5">
-        <f>AVERAGE(B5:B9)</f>
-        <v/>
+      <c r="E9" s="5" t="n">
+        <v>7137.11</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7137.11</v>
       </c>
       <c r="G9" s="6">
         <f>(B9-6528.52)/6528.52</f>
@@ -4071,13 +4069,11 @@
         <f>(B10-B9)/B9</f>
         <v/>
       </c>
-      <c r="E10" s="10">
-        <f>AVERAGE(B6:B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="10">
-        <f>AVERAGE(B5:B10)</f>
-        <v/>
+      <c r="E10" s="10" t="n">
+        <v>7101.41</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>7123.97</v>
       </c>
       <c r="G10" s="11">
         <f>(B10-6528.52)/6528.52</f>
@@ -4116,13 +4112,11 @@
         <f>(B11-B10)/B10</f>
         <v/>
       </c>
-      <c r="E11" s="10">
-        <f>AVERAGE(B7:B11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="10">
-        <f>AVERAGE(B5:B11)</f>
-        <v/>
+      <c r="E11" s="10" t="n">
+        <v>7155.9</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>7141.52</v>
       </c>
       <c r="G11" s="11">
         <f>(B11-6528.52)/6528.52</f>
@@ -4161,13 +4155,11 @@
         <f>(B12-B11)/B11</f>
         <v/>
       </c>
-      <c r="E12" s="10">
-        <f>AVERAGE(B8:B12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>AVERAGE(B6:B12)</f>
-        <v/>
+      <c r="E12" s="10" t="n">
+        <v>7122.17</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>7099.98</v>
       </c>
       <c r="G12" s="11">
         <f>(B12-6528.52)/6528.52</f>
@@ -4206,13 +4198,11 @@
         <f>(B13-B12)/B12</f>
         <v/>
       </c>
-      <c r="E13" s="10">
-        <f>AVERAGE(B9:B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>AVERAGE(B7:B13)</f>
-        <v/>
+      <c r="E13" s="10" t="n">
+        <v>7160.04</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>7146.45</v>
       </c>
       <c r="G13" s="11">
         <f>(B13-6528.52)/6528.52</f>
@@ -4251,13 +4241,11 @@
         <f>(B14-B13)/B13</f>
         <v/>
       </c>
-      <c r="E14" s="10">
-        <f>AVERAGE(B10:B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>AVERAGE(B8:B14)</f>
-        <v/>
+      <c r="E14" s="10" t="n">
+        <v>7184.46</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>7169.26</v>
       </c>
       <c r="G14" s="11">
         <f>(B14-6528.52)/6528.52</f>
@@ -4296,13 +4284,11 @@
         <f>(B15-B14)/B14</f>
         <v/>
       </c>
-      <c r="E15" s="10">
-        <f>AVERAGE(B11:B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
-        <f>AVERAGE(B9:B15)</f>
-        <v/>
+      <c r="E15" s="10" t="n">
+        <v>7187.33</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>7182.91</v>
       </c>
       <c r="G15" s="11">
         <f>(B15-6528.52)/6528.52</f>
@@ -4341,13 +4327,11 @@
         <f>(B16-B15)/B15</f>
         <v/>
       </c>
-      <c r="E16" s="10">
-        <f>AVERAGE(B12:B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>AVERAGE(B10:B16)</f>
-        <v/>
+      <c r="E16" s="10" t="n">
+        <v>7197.59</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>7199.01</v>
       </c>
       <c r="G16" s="11">
         <f>(B16-6528.52)/6528.52</f>
@@ -4382,9 +4366,15 @@
       <c r="D17" s="18" t="n">
         <v>0.0146</v>
       </c>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
+      <c r="E17" s="42" t="n">
+        <v>7242.04</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>7217.15</v>
+      </c>
+      <c r="G17" s="43" t="n">
+        <v>0.0294</v>
+      </c>
       <c r="H17" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4412,9 +4402,15 @@
       </c>
       <c r="C18" s="18" t="n"/>
       <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
+      <c r="E18" s="42" t="n">
+        <v>7293.44</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <v>7251.17</v>
+      </c>
+      <c r="G18" s="43" t="n">
+        <v>0.0359</v>
+      </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4442,9 +4438,15 @@
       </c>
       <c r="C19" s="18" t="n"/>
       <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
+      <c r="E19" s="42" t="n">
+        <v>7347.7</v>
+      </c>
+      <c r="F19" s="42" t="n">
+        <v>7303.37</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <v>0.0484</v>
+      </c>
       <c r="H19" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4474,9 +4476,15 @@
       <c r="D20" s="18" t="n">
         <v>0.0026</v>
       </c>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
+      <c r="E20" s="42" t="n">
+        <v>7427.54</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <v>7366.94</v>
+      </c>
+      <c r="G20" s="43" t="n">
+        <v>0.0622</v>
+      </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4506,9 +4514,15 @@
       <c r="D21" s="18" t="n">
         <v>0.0013</v>
       </c>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
+      <c r="E21" s="42" t="n">
+        <v>7497.65</v>
+      </c>
+      <c r="F21" s="42" t="n">
+        <v>7421.17</v>
+      </c>
+      <c r="G21" s="43" t="n">
+        <v>0.0013</v>
+      </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4536,9 +4550,15 @@
       </c>
       <c r="C22" s="41" t="n"/>
       <c r="D22" s="41" t="n"/>
-      <c r="E22" s="41" t="n"/>
-      <c r="F22" s="41" t="n"/>
-      <c r="G22" s="41" t="n"/>
+      <c r="E22" s="44" t="n">
+        <v>7541.42</v>
+      </c>
+      <c r="F22" s="44" t="n">
+        <v>7475.92</v>
+      </c>
+      <c r="G22" s="45" t="n">
+        <v>-0.0021</v>
+      </c>
       <c r="H22" s="41" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4568,9 +4588,15 @@
       <c r="D23" s="19" t="n">
         <v>-0.0264</v>
       </c>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
+      <c r="E23" s="46" t="n">
+        <v>7535.76</v>
+      </c>
+      <c r="F23" s="46" t="n">
+        <v>7493.71</v>
+      </c>
+      <c r="G23" s="47" t="n">
+        <v>-0.0285</v>
+      </c>
       <c r="H23" s="19" t="inlineStr">
         <is>
           <t>SELL</t>
@@ -4602,9 +4628,15 @@
       <c r="D24" s="41" t="n">
         <v>0.003</v>
       </c>
-      <c r="E24" s="41" t="n"/>
-      <c r="F24" s="41" t="n"/>
-      <c r="G24" s="41" t="n"/>
+      <c r="E24" s="44" t="n">
+        <v>7516.63</v>
+      </c>
+      <c r="F24" s="44" t="n">
+        <v>7499.51</v>
+      </c>
+      <c r="G24" s="45" t="n">
+        <v>-0.0256</v>
+      </c>
       <c r="H24" s="41" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4636,9 +4668,15 @@
       <c r="D25" s="41" t="n">
         <v>-0.0026</v>
       </c>
-      <c r="E25" s="41" t="n"/>
-      <c r="F25" s="41" t="n"/>
-      <c r="G25" s="41" t="n"/>
+      <c r="E25" s="44" t="n">
+        <v>7473.97</v>
+      </c>
+      <c r="F25" s="44" t="n">
+        <v>7495.89</v>
+      </c>
+      <c r="G25" s="45" t="n">
+        <v>-0.0281</v>
+      </c>
       <c r="H25" s="41" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4670,9 +4708,15 @@
       <c r="D26" s="41" t="n">
         <v>-0.0162</v>
       </c>
-      <c r="E26" s="41" t="n"/>
-      <c r="F26" s="41" t="n"/>
-      <c r="G26" s="41" t="n"/>
+      <c r="E26" s="44" t="n">
+        <v>7405.41</v>
+      </c>
+      <c r="F26" s="44" t="n">
+        <v>7462.4</v>
+      </c>
+      <c r="G26" s="45" t="n">
+        <v>-0.0438</v>
+      </c>
       <c r="H26" s="41" t="inlineStr">
         <is>
           <t>SELL</t>
@@ -4704,9 +4748,15 @@
       <c r="D27" s="41" t="n">
         <v>0.0175</v>
       </c>
-      <c r="E27" s="41" t="n"/>
-      <c r="F27" s="41" t="n"/>
-      <c r="G27" s="41" t="n"/>
+      <c r="E27" s="44" t="n">
+        <v>7367.48</v>
+      </c>
+      <c r="F27" s="44" t="n">
+        <v>7433.02</v>
+      </c>
+      <c r="G27" s="45" t="n">
+        <v>-0.0271</v>
+      </c>
       <c r="H27" s="41" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4738,9 +4788,15 @@
       <c r="D28" s="41" t="n">
         <v>0.005</v>
       </c>
-      <c r="E28" s="41" t="n"/>
-      <c r="F28" s="41" t="n"/>
-      <c r="G28" s="41" t="n"/>
+      <c r="E28" s="44" t="n">
+        <v>7377.03</v>
+      </c>
+      <c r="F28" s="44" t="n">
+        <v>7407.55</v>
+      </c>
+      <c r="G28" s="45" t="n">
+        <v>-0.0222</v>
+      </c>
       <c r="H28" s="41" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4772,9 +4828,15 @@
       <c r="D29" s="41" t="n">
         <v>0.0165</v>
       </c>
-      <c r="E29" s="41" t="n"/>
-      <c r="F29" s="41" t="n"/>
-      <c r="G29" s="41" t="n"/>
+      <c r="E29" s="44" t="n">
+        <v>7406.74</v>
+      </c>
+      <c r="F29" s="44" t="n">
+        <v>7403.31</v>
+      </c>
+      <c r="G29" s="45" t="n">
+        <v>-0.006</v>
+      </c>
       <c r="H29" s="41" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4806,9 +4868,15 @@
       <c r="D30" s="41" t="n">
         <v>-0.0057</v>
       </c>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="41" t="n"/>
+      <c r="E30" s="44" t="n">
+        <v>7431.6</v>
+      </c>
+      <c r="F30" s="44" t="n">
+        <v>7421.49</v>
+      </c>
+      <c r="G30" s="45" t="n">
+        <v>-0.0117</v>
+      </c>
       <c r="H30" s="41" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4838,9 +4906,15 @@
       <c r="D31" s="19" t="n">
         <v>-0.0121</v>
       </c>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
+      <c r="E31" s="46" t="n">
+        <v>7462.23</v>
+      </c>
+      <c r="F31" s="46" t="n">
+        <v>7423.54</v>
+      </c>
+      <c r="G31" s="47" t="n">
+        <v>-0.0237</v>
+      </c>
       <c r="H31" s="19" t="inlineStr">
         <is>
           <t>SELL</t>
@@ -4872,9 +4946,15 @@
       <c r="D32" s="19" t="n">
         <v>0.0108</v>
       </c>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="19" t="n"/>
-      <c r="G32" s="19" t="n"/>
+      <c r="E32" s="46" t="n">
+        <v>7483.48</v>
+      </c>
+      <c r="F32" s="46" t="n">
+        <v>7439.81</v>
+      </c>
+      <c r="G32" s="47" t="n">
+        <v>-0.0131</v>
+      </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -4906,6 +4986,15 @@
       <c r="D33" t="n">
         <v>0.0012</v>
       </c>
+      <c r="E33" s="48" t="n">
+        <v>7498.99</v>
+      </c>
+      <c r="F33" s="48" t="n">
+        <v>7474.39</v>
+      </c>
+      <c r="G33" s="49" t="n">
+        <v>-0.012</v>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4937,6 +5026,15 @@
       <c r="D34" t="n">
         <v>-0.0144</v>
       </c>
+      <c r="E34" s="48" t="n">
+        <v>7461.22</v>
+      </c>
+      <c r="F34" s="48" t="n">
+        <v>7470.27</v>
+      </c>
+      <c r="G34" s="49" t="n">
+        <v>-0.0309</v>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>SELL</t>
@@ -4968,6 +5066,15 @@
       <c r="D35" t="n">
         <v>-0.001</v>
       </c>
+      <c r="E35" s="48" t="n">
+        <v>7430.67</v>
+      </c>
+      <c r="F35" s="48" t="n">
+        <v>7459.8</v>
+      </c>
+      <c r="G35" s="49" t="n">
+        <v>-0.0318</v>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4999,6 +5106,15 @@
       <c r="D36" t="n">
         <v>-0.0001</v>
       </c>
+      <c r="E36" s="48" t="n">
+        <v>7418.15</v>
+      </c>
+      <c r="F36" s="48" t="n">
+        <v>7431.69</v>
+      </c>
+      <c r="G36" s="49" t="n">
+        <v>-0.0319</v>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -5027,6 +5143,15 @@
       <c r="D37" t="n">
         <v>0.012</v>
       </c>
+      <c r="E37" s="48" t="n">
+        <v>7407.03</v>
+      </c>
+      <c r="F37" s="48" t="n">
+        <v>7422.26</v>
+      </c>
+      <c r="G37" s="49" t="n">
+        <v>-0.0204</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -5058,6 +5183,15 @@
       <c r="D38" t="n">
         <v>0.0003</v>
       </c>
+      <c r="E38" s="48" t="n">
+        <v>7395.11</v>
+      </c>
+      <c r="F38" s="48" t="n">
+        <v>7426.44</v>
+      </c>
+      <c r="G38" s="49" t="n">
+        <v>-0.0198</v>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -5086,6 +5220,15 @@
       <c r="D39" t="n">
         <v>0.0045</v>
       </c>
+      <c r="E39" s="48" t="n">
+        <v>7418.61</v>
+      </c>
+      <c r="F39" s="48" t="n">
+        <v>7423.93</v>
+      </c>
+      <c r="G39" s="49" t="n">
+        <v>0.0045</v>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -5113,6 +5256,15 @@
       </c>
       <c r="D40" t="n">
         <v>-0.0039</v>
+      </c>
+      <c r="E40" s="48" t="n">
+        <v>7437.76</v>
+      </c>
+      <c r="F40" s="48" t="n">
+        <v>7416.07</v>
+      </c>
+      <c r="G40" s="49" t="n">
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5143,9 +5295,15 @@
       <c r="D41" s="41" t="n">
         <v>0.0072</v>
       </c>
-      <c r="E41" s="41" t="n"/>
-      <c r="F41" s="41" t="n"/>
-      <c r="G41" s="41" t="n"/>
+      <c r="E41" s="44" t="n">
+        <v>7473.75</v>
+      </c>
+      <c r="F41" s="44" t="n">
+        <v>7440.64</v>
+      </c>
+      <c r="G41" s="45" t="n">
+        <v>0.0118</v>
+      </c>
       <c r="H41" s="41" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -5177,9 +5335,15 @@
       <c r="D42" s="41" t="n">
         <v>-0.0045</v>
       </c>
-      <c r="E42" s="41" t="n"/>
-      <c r="F42" s="41" t="n"/>
-      <c r="G42" s="41" t="n"/>
+      <c r="E42" s="44" t="n">
+        <v>7485.52</v>
+      </c>
+      <c r="F42" s="44" t="n">
+        <v>7461.44</v>
+      </c>
+      <c r="G42" s="45" t="n">
+        <v>0.0073</v>
+      </c>
       <c r="H42" s="41" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -5211,9 +5375,15 @@
       <c r="D43" s="41" t="n">
         <v>-0.0028</v>
       </c>
-      <c r="E43" s="41" t="n"/>
-      <c r="F43" s="41" t="n"/>
-      <c r="G43" s="41" t="n"/>
+      <c r="E43" s="44" t="n">
+        <v>7492.19</v>
+      </c>
+      <c r="F43" s="44" t="n">
+        <v>7479.33</v>
+      </c>
+      <c r="G43" s="45" t="n">
+        <v>0.0045</v>
+      </c>
       <c r="H43" s="41" t="inlineStr">
         <is>
           <t>SELL</t>
@@ -5245,9 +5415,15 @@
       <c r="D44" s="41" t="n">
         <v>0.0081</v>
       </c>
-      <c r="E44" s="41" t="n"/>
-      <c r="F44" s="41" t="n"/>
-      <c r="G44" s="41" t="n"/>
+      <c r="E44" s="44" t="n">
+        <v>7504.32</v>
+      </c>
+      <c r="F44" s="44" t="n">
+        <v>7493.42</v>
+      </c>
+      <c r="G44" s="45" t="n">
+        <v>0.0127</v>
+      </c>
       <c r="H44" s="41" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -5279,9 +5455,15 @@
       <c r="D45" s="41" t="n">
         <v>0.0042</v>
       </c>
-      <c r="E45" s="41" t="n"/>
-      <c r="F45" s="41" t="n"/>
-      <c r="G45" s="41" t="n"/>
+      <c r="E45" s="44" t="n">
+        <v>7528.6</v>
+      </c>
+      <c r="F45" s="44" t="n">
+        <v>7511.43</v>
+      </c>
+      <c r="G45" s="45" t="n">
+        <v>0.0169</v>
+      </c>
       <c r="H45" s="41" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -5313,9 +5495,15 @@
       <c r="D46" s="41" t="n">
         <v>-0.008</v>
       </c>
-      <c r="E46" s="41" t="n"/>
-      <c r="F46" s="41" t="n"/>
-      <c r="G46" s="41" t="n"/>
+      <c r="E46" s="44" t="n">
+        <v>7524.12</v>
+      </c>
+      <c r="F46" s="44" t="n">
+        <v>7516</v>
+      </c>
+      <c r="G46" s="45" t="n">
+        <v>0.008800000000000001</v>
+      </c>
       <c r="H46" s="41" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -5347,9 +5535,15 @@
       <c r="D47" s="41" t="n">
         <v>0.0038</v>
       </c>
-      <c r="E47" s="41" t="n"/>
-      <c r="F47" s="41" t="n"/>
-      <c r="G47" s="41" t="n"/>
+      <c r="E47" s="44" t="n">
+        <v>7532.07</v>
+      </c>
+      <c r="F47" s="44" t="n">
+        <v>7528.81</v>
+      </c>
+      <c r="G47" s="45" t="n">
+        <v>0.0126</v>
+      </c>
       <c r="H47" s="41" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -5381,9 +5575,15 @@
       <c r="D48" s="41" t="n">
         <v>-0.0051</v>
       </c>
-      <c r="E48" s="41" t="n"/>
-      <c r="F48" s="41" t="n"/>
-      <c r="G48" s="41" t="n"/>
+      <c r="E48" s="44" t="n">
+        <v>7542.28</v>
+      </c>
+      <c r="F48" s="44" t="n">
+        <v>7528.28</v>
+      </c>
+      <c r="G48" s="45" t="n">
+        <v>0.0113</v>
+      </c>
       <c r="H48" s="41" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -5443,9 +5643,15 @@
       <c r="D50" s="41" t="n">
         <v>-0.0102</v>
       </c>
-      <c r="E50" s="41" t="n"/>
-      <c r="F50" s="41" t="n"/>
-      <c r="G50" s="41" t="n"/>
+      <c r="E50" s="44" t="n">
+        <v>7524.96</v>
+      </c>
+      <c r="F50" s="44" t="n">
+        <v>7521.59</v>
+      </c>
+      <c r="G50" s="45" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H50" s="41" t="inlineStr">
         <is>
           <t>SELL</t>
@@ -7861,7 +8067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.609375" defaultRowHeight="15"/>
   <cols>
     <col width="89.99609375" customWidth="1" style="37" min="1" max="1"/>
@@ -8068,7 +8274,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -8122,6 +8327,42 @@
       <c r="A41" t="inlineStr">
         <is>
           <t>- Blue-filled rows = added in the Jul 21 finalization pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MA / MTD% methodology (added 2026-07-21):</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>- 5-Day / 7-Day MA after May 5 = average of the trailing 5/7 LOGGED closes (series has source gaps; not strictly consecutive trading days).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>- MTD% baselines: Apr vs Mar 31 (6,528.52); May vs Apr 30 (7,155); Jun vs May 28 (7,599.96 - last logged May close, May 29 close unpublished); Jul vs Jun 30 (7,449.36).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>- MA/MTD left blank on rows without a numeric close (Jul 16, Jul 20, holidays, PENDING).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>- MA/MTD% values computed at finalization (static values; environment could not run a live recalc engine).</t>
         </is>
       </c>
     </row>

--- a/MI_PE_Tracking_System.xlsx
+++ b/MI_PE_Tracking_System.xlsx
@@ -1409,10 +1409,26 @@
       <c r="C18" s="20" t="n">
         <v>0.0146</v>
       </c>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="20" t="n"/>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
           <t>Tech steady</t>
@@ -1458,11 +1474,31 @@
       <c r="B19" s="20" t="n">
         <v>7412</v>
       </c>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
           <t>AI leadership continues</t>
@@ -1508,11 +1544,31 @@
       <c r="B20" s="20" t="n">
         <v>7501.39</v>
       </c>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="20" t="n"/>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
           <t>Chip/AI strength</t>
@@ -1560,15 +1616,31 @@
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C21" s="40" t="n"/>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="E21" s="40" t="n"/>
-      <c r="F21" s="40" t="n"/>
-      <c r="G21" s="40" t="n"/>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="H21" s="40" t="inlineStr">
         <is>
           <t>—</t>
@@ -1611,12 +1683,36 @@
           <t>May 27 2026</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
           <t>Micron joins $1T market-cap club</t>
@@ -1665,10 +1761,26 @@
       <c r="C23" s="20" t="n">
         <v>0.0026</v>
       </c>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
           <t>AI rally broadens</t>
@@ -1711,14 +1823,34 @@
           <t>May 29 2026</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="D24" s="20" t="n">
         <v>26972.62</v>
       </c>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
           <t>Nasdaq intraday high 26,972.62</t>
@@ -1761,12 +1893,36 @@
           <t>Jun 1 2026</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Tech rally overpowers oil spike</t>
@@ -1815,10 +1971,26 @@
       <c r="C26" s="21" t="n">
         <v>0.0013</v>
       </c>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
           <t>AI/chip melt-up</t>
@@ -1864,11 +2036,31 @@
       <c r="B27" s="40" t="n">
         <v>7583.95</v>
       </c>
-      <c r="C27" s="40" t="n"/>
-      <c r="D27" s="40" t="n"/>
-      <c r="E27" s="40" t="n"/>
-      <c r="F27" s="40" t="n"/>
-      <c r="G27" s="40" t="n"/>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D27" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E27" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H27" s="40" t="inlineStr">
         <is>
           <t>Near-record into chip rout</t>
@@ -1917,8 +2109,16 @@
       <c r="C28" s="21" t="n">
         <v>-0.0264</v>
       </c>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="F28" s="21" t="n">
         <v>93.45</v>
       </c>
@@ -1973,10 +2173,26 @@
       <c r="C29" s="40" t="n">
         <v>0.003</v>
       </c>
-      <c r="D29" s="40" t="n"/>
-      <c r="E29" s="40" t="n"/>
-      <c r="F29" s="40" t="n"/>
-      <c r="G29" s="40" t="n"/>
+      <c r="D29" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H29" s="40" t="inlineStr">
         <is>
           <t>Chip rebound fails to hold</t>
@@ -2025,10 +2241,26 @@
       <c r="C30" s="40" t="n">
         <v>-0.0026</v>
       </c>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H30" s="40" t="inlineStr">
         <is>
           <t>Chip surge loses momentum</t>
@@ -2077,10 +2309,26 @@
       <c r="C31" s="40" t="n">
         <v>-0.0162</v>
       </c>
-      <c r="D31" s="40" t="n"/>
-      <c r="E31" s="40" t="n"/>
-      <c r="F31" s="40" t="n"/>
-      <c r="G31" s="40" t="n"/>
+      <c r="D31" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E31" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H31" s="40" t="inlineStr">
         <is>
           <t>Selloff deepens</t>
@@ -2129,10 +2377,26 @@
       <c r="C32" s="40" t="n">
         <v>0.0175</v>
       </c>
-      <c r="D32" s="40" t="n"/>
-      <c r="E32" s="40" t="n"/>
-      <c r="F32" s="40" t="n"/>
-      <c r="G32" s="40" t="n"/>
+      <c r="D32" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H32" s="40" t="inlineStr">
         <is>
           <t>Sharp rebound</t>
@@ -2181,10 +2445,26 @@
       <c r="C33" s="40" t="n">
         <v>0.005</v>
       </c>
-      <c r="D33" s="40" t="n"/>
-      <c r="E33" s="40" t="n"/>
-      <c r="F33" s="40" t="n"/>
-      <c r="G33" s="40" t="n"/>
+      <c r="D33" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H33" s="40" t="inlineStr">
         <is>
           <t>Recovery extends</t>
@@ -2233,10 +2513,26 @@
       <c r="C34" s="40" t="n">
         <v>0.0165</v>
       </c>
-      <c r="D34" s="40" t="n"/>
-      <c r="E34" s="40" t="n"/>
-      <c r="F34" s="40" t="n"/>
-      <c r="G34" s="40" t="n"/>
+      <c r="D34" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H34" s="40" t="inlineStr">
         <is>
           <t>SpaceX rally extends</t>
@@ -2285,10 +2581,26 @@
       <c r="C35" s="40" t="n">
         <v>-0.0057</v>
       </c>
-      <c r="D35" s="40" t="n"/>
-      <c r="E35" s="40" t="n"/>
-      <c r="F35" s="40" t="n"/>
-      <c r="G35" s="40" t="n"/>
+      <c r="D35" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E35" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H35" s="40" t="inlineStr">
         <is>
           <t>Warsh first-meeting jitters</t>
@@ -2343,8 +2655,16 @@
       <c r="E36" s="21" t="n">
         <v>-0.0134</v>
       </c>
-      <c r="F36" s="21" t="n"/>
-      <c r="G36" s="21" t="n"/>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H36" s="21" t="inlineStr">
         <is>
           <t>Chips slide into Fed day</t>
@@ -2399,8 +2719,16 @@
       <c r="E37" s="21" t="n">
         <v>0.015</v>
       </c>
-      <c r="F37" s="21" t="n"/>
-      <c r="G37" s="21" t="n"/>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Chips fuel comeback</t>
@@ -2448,15 +2776,31 @@
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C38" s="21" t="n"/>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="21" t="n"/>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="H38" s="21" t="inlineStr">
         <is>
           <t>—</t>
@@ -2499,10 +2843,26 @@
           <t>Jun 20 2026</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="F39" s="21" t="n">
         <v>77.54000000000001</v>
       </c>
@@ -2683,6 +3043,16 @@
       <c r="E42" t="n">
         <v>-0.0043</v>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Chips slide ahead of Micron</t>
@@ -2737,6 +3107,16 @@
       <c r="E43" t="n">
         <v>-0.0046</v>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Tech soft</t>
@@ -2779,9 +3159,34 @@
           <t>Jun 26 2026</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="F44" t="n">
         <v>69.5</v>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Tread water amid tech sell-off</t>
@@ -2830,9 +3235,19 @@
       <c r="C45" t="n">
         <v>0.012</v>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="E45" t="n">
         <v>0.02</v>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="G45" t="n">
         <v>73.17</v>
       </c>
@@ -2890,6 +3305,16 @@
       <c r="E46" t="n">
         <v>0.0029</v>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Nasdaq +0.29%</t>
@@ -2938,6 +3363,16 @@
       <c r="C47" t="n">
         <v>0.0045</v>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="F47" t="n">
         <v>68.58</v>
       </c>
@@ -2992,9 +3427,17 @@
       <c r="C48" t="n">
         <v>-0.0039</v>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="E48" t="n">
         <v>-0.0118</v>
       </c>
+      <c r="F48" t="n">
+        <v>68</v>
+      </c>
       <c r="G48" t="n">
         <v>68</v>
       </c>
@@ -3045,15 +3488,31 @@
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C49" s="41" t="n"/>
+      <c r="C49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D49" s="41" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="E49" s="41" t="n"/>
-      <c r="F49" s="41" t="n"/>
-      <c r="G49" s="41" t="n"/>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="H49" s="41" t="inlineStr">
         <is>
           <t>—</t>
@@ -3108,8 +3567,16 @@
       <c r="E50" s="41" t="n">
         <v>0.0112</v>
       </c>
-      <c r="F50" s="41" t="n"/>
-      <c r="G50" s="41" t="n"/>
+      <c r="F50" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G50" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H50" s="41" t="inlineStr">
         <is>
           <t>AI optimism revives</t>
@@ -3164,8 +3631,16 @@
       <c r="E51" s="41" t="n">
         <v>-0.0116</v>
       </c>
-      <c r="F51" s="41" t="n"/>
-      <c r="G51" s="41" t="n"/>
+      <c r="F51" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G51" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H51" s="41" t="inlineStr">
         <is>
           <t>Tech gives back</t>
@@ -3214,8 +3689,16 @@
       <c r="C52" s="41" t="n">
         <v>-0.0028</v>
       </c>
-      <c r="D52" s="41" t="n"/>
-      <c r="E52" s="41" t="n"/>
+      <c r="D52" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E52" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="F52" s="41" t="n">
         <v>73.52</v>
       </c>
@@ -3270,10 +3753,26 @@
       <c r="C53" s="41" t="n">
         <v>0.0081</v>
       </c>
-      <c r="D53" s="41" t="n"/>
-      <c r="E53" s="41" t="n"/>
-      <c r="F53" s="41" t="n"/>
-      <c r="G53" s="41" t="n"/>
+      <c r="D53" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E53" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F53" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G53" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H53" s="41" t="inlineStr">
         <is>
           <t>Semis jump</t>
@@ -3328,8 +3827,16 @@
       <c r="E54" s="41" t="n">
         <v>0.0029</v>
       </c>
-      <c r="F54" s="41" t="n"/>
-      <c r="G54" s="41" t="n"/>
+      <c r="F54" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G54" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H54" s="41" t="inlineStr">
         <is>
           <t>Tech-led winning week</t>
@@ -3378,10 +3885,26 @@
       <c r="C55" s="41" t="n">
         <v>-0.008</v>
       </c>
-      <c r="D55" s="41" t="n"/>
-      <c r="E55" s="41" t="n"/>
-      <c r="F55" s="41" t="n"/>
-      <c r="G55" s="41" t="n"/>
+      <c r="D55" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E55" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F55" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G55" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H55" s="41" t="inlineStr">
         <is>
           <t>Drift lower</t>
@@ -3436,8 +3959,16 @@
       <c r="E56" s="41" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="F56" s="41" t="n"/>
-      <c r="G56" s="41" t="n"/>
+      <c r="F56" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G56" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H56" s="41" t="inlineStr">
         <is>
           <t>Nasdaq +0.9%</t>
@@ -3492,8 +4023,16 @@
       <c r="E57" s="41" t="n">
         <v>-0.0147</v>
       </c>
-      <c r="F57" s="41" t="n"/>
-      <c r="G57" s="41" t="n"/>
+      <c r="F57" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G57" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H57" s="41" t="inlineStr">
         <is>
           <t>Alphabet &amp; chips sell off; SpaceX below IPO price</t>
@@ -3536,16 +4075,32 @@
           <t>Jul 16 2026</t>
         </is>
       </c>
-      <c r="B58" s="41" t="n"/>
+      <c r="B58" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="C58" s="41" t="n">
         <v>-0.0037</v>
       </c>
-      <c r="D58" s="41" t="n"/>
+      <c r="D58" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="E58" s="41" t="n">
         <v>-0.0076</v>
       </c>
-      <c r="F58" s="41" t="n"/>
-      <c r="G58" s="41" t="n"/>
+      <c r="F58" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G58" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H58" s="41" t="inlineStr">
         <is>
           <t>Semiconductor slide continues</t>
@@ -3600,8 +4155,16 @@
       <c r="E59" s="41" t="n">
         <v>-0.014</v>
       </c>
-      <c r="F59" s="41" t="n"/>
-      <c r="G59" s="41" t="n"/>
+      <c r="F59" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G59" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H59" s="41" t="inlineStr">
         <is>
           <t>MOONSHOT AI SHOCK: Chinese startup rivals US models; global tech rout</t>
@@ -3644,11 +4207,31 @@
           <t>Jul 20 2026</t>
         </is>
       </c>
-      <c r="B60" s="41" t="n"/>
-      <c r="C60" s="41" t="n"/>
-      <c r="D60" s="41" t="n"/>
-      <c r="E60" s="41" t="n"/>
-      <c r="F60" s="41" t="n"/>
+      <c r="B60" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C60" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D60" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E60" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F60" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="G60" s="41" t="n">
         <v>90</v>
       </c>
@@ -3699,15 +4282,31 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="C61" s="41" t="n"/>
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D61" s="41" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="E61" s="41" t="n"/>
-      <c r="F61" s="41" t="n"/>
-      <c r="G61" s="41" t="n"/>
+      <c r="E61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="H61" s="41" t="inlineStr">
         <is>
           <t>—</t>
@@ -3860,9 +4459,8 @@
       <c r="F5" s="5" t="n">
         <v>7109.14</v>
       </c>
-      <c r="G5" s="6">
-        <f>(B5-6528.52)/6528.52</f>
-        <v/>
+      <c r="G5" s="6" t="n">
+        <v>0.08890000000000001</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -3889,13 +4487,11 @@
       <c r="B6" s="5" t="n">
         <v>7064.01</v>
       </c>
-      <c r="C6" s="5">
-        <f>B6-B5</f>
-        <v/>
-      </c>
-      <c r="D6" s="6">
-        <f>(B6-B5)/B5</f>
-        <v/>
+      <c r="C6" s="5" t="n">
+        <v>-45.13</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>7086.58</v>
@@ -3903,9 +4499,8 @@
       <c r="F6" s="5" t="n">
         <v>7086.58</v>
       </c>
-      <c r="G6" s="6">
-        <f>(B6-6528.52)/6528.52</f>
-        <v/>
+      <c r="G6" s="6" t="n">
+        <v>0.082</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -3932,13 +4527,11 @@
       <c r="B7" s="5" t="n">
         <v>7137.9</v>
       </c>
-      <c r="C7" s="5">
-        <f>B7-B6</f>
-        <v/>
-      </c>
-      <c r="D7" s="6">
-        <f>(B7-B6)/B6</f>
-        <v/>
+      <c r="C7" s="5" t="n">
+        <v>73.89</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.0105</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>7123.52</v>
@@ -3946,9 +4539,8 @@
       <c r="F7" s="5" t="n">
         <v>7123.52</v>
       </c>
-      <c r="G7" s="6">
-        <f>(B7-6528.52)/6528.52</f>
-        <v/>
+      <c r="G7" s="6" t="n">
+        <v>0.09329999999999999</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -3975,13 +4567,11 @@
       <c r="B8" s="5" t="n">
         <v>7108.4</v>
       </c>
-      <c r="C8" s="5">
-        <f>B8-B7</f>
-        <v/>
-      </c>
-      <c r="D8" s="6">
-        <f>(B8-B7)/B7</f>
-        <v/>
+      <c r="C8" s="5" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.0041</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>7108.77</v>
@@ -3989,9 +4579,8 @@
       <c r="F8" s="5" t="n">
         <v>7108.77</v>
       </c>
-      <c r="G8" s="6">
-        <f>(B8-6528.52)/6528.52</f>
-        <v/>
+      <c r="G8" s="6" t="n">
+        <v>0.0888</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -4018,13 +4607,11 @@
       <c r="B9" s="5" t="n">
         <v>7165.08</v>
       </c>
-      <c r="C9" s="5">
-        <f>B9-B8</f>
-        <v/>
-      </c>
-      <c r="D9" s="6">
-        <f>(B9-B8)/B8</f>
-        <v/>
+      <c r="C9" s="5" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.008</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>7137.11</v>
@@ -4032,9 +4619,8 @@
       <c r="F9" s="5" t="n">
         <v>7137.11</v>
       </c>
-      <c r="G9" s="6">
-        <f>(B9-6528.52)/6528.52</f>
-        <v/>
+      <c r="G9" s="6" t="n">
+        <v>0.0975</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -4061,13 +4647,11 @@
       <c r="B10" s="10" t="n">
         <v>7138.8</v>
       </c>
-      <c r="C10" s="10">
-        <f>B10-B9</f>
-        <v/>
-      </c>
-      <c r="D10" s="11">
-        <f>(B10-B9)/B9</f>
-        <v/>
+      <c r="C10" s="10" t="n">
+        <v>-26.28</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>7101.41</v>
@@ -4075,9 +4659,8 @@
       <c r="F10" s="10" t="n">
         <v>7123.97</v>
       </c>
-      <c r="G10" s="11">
-        <f>(B10-6528.52)/6528.52</f>
-        <v/>
+      <c r="G10" s="11" t="n">
+        <v>0.0935</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -4104,13 +4687,11 @@
       <c r="B11" s="10" t="n">
         <v>7173.91</v>
       </c>
-      <c r="C11" s="10">
-        <f>B11-B10</f>
-        <v/>
-      </c>
-      <c r="D11" s="11">
-        <f>(B11-B10)/B10</f>
-        <v/>
+      <c r="C11" s="10" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>0.0049</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>7155.9</v>
@@ -4118,9 +4699,8 @@
       <c r="F11" s="10" t="n">
         <v>7141.52</v>
       </c>
-      <c r="G11" s="11">
-        <f>(B11-6528.52)/6528.52</f>
-        <v/>
+      <c r="G11" s="11" t="n">
+        <v>0.0989</v>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -4147,13 +4727,11 @@
       <c r="B12" s="10" t="n">
         <v>7135.95</v>
       </c>
-      <c r="C12" s="10">
-        <f>B12-B11</f>
-        <v/>
-      </c>
-      <c r="D12" s="11">
-        <f>(B12-B11)/B11</f>
-        <v/>
+      <c r="C12" s="10" t="n">
+        <v>-37.96</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>7122.17</v>
@@ -4161,9 +4739,8 @@
       <c r="F12" s="10" t="n">
         <v>7099.98</v>
       </c>
-      <c r="G12" s="11">
-        <f>(B12-6528.52)/6528.52</f>
-        <v/>
+      <c r="G12" s="11" t="n">
+        <v>0.093</v>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
@@ -4190,13 +4767,11 @@
       <c r="B13" s="10" t="n">
         <v>7155</v>
       </c>
-      <c r="C13" s="10">
-        <f>B13-B12</f>
-        <v/>
-      </c>
-      <c r="D13" s="11">
-        <f>(B13-B12)/B12</f>
-        <v/>
+      <c r="C13" s="10" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>0.0027</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>7160.04</v>
@@ -4204,9 +4779,8 @@
       <c r="F13" s="10" t="n">
         <v>7146.45</v>
       </c>
-      <c r="G13" s="11">
-        <f>(B13-6528.52)/6528.52</f>
-        <v/>
+      <c r="G13" s="11" t="n">
+        <v>0.096</v>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
@@ -4233,13 +4807,11 @@
       <c r="B14" s="10" t="n">
         <v>7230.12</v>
       </c>
-      <c r="C14" s="10">
-        <f>B14-B13</f>
-        <v/>
-      </c>
-      <c r="D14" s="11">
-        <f>(B14-B13)/B13</f>
-        <v/>
+      <c r="C14" s="10" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>0.0105</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>7184.46</v>
@@ -4247,9 +4819,8 @@
       <c r="F14" s="10" t="n">
         <v>7169.26</v>
       </c>
-      <c r="G14" s="11">
-        <f>(B14-6528.52)/6528.52</f>
-        <v/>
+      <c r="G14" s="11" t="n">
+        <v>0.1075</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
@@ -4276,13 +4847,11 @@
       <c r="B15" s="10" t="n">
         <v>7200.75</v>
       </c>
-      <c r="C15" s="10">
-        <f>B15-B14</f>
-        <v/>
-      </c>
-      <c r="D15" s="11">
-        <f>(B15-B14)/B14</f>
-        <v/>
+      <c r="C15" s="10" t="n">
+        <v>-29.37</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>-0.0041</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>7187.33</v>
@@ -4290,9 +4859,8 @@
       <c r="F15" s="10" t="n">
         <v>7182.91</v>
       </c>
-      <c r="G15" s="11">
-        <f>(B15-6528.52)/6528.52</f>
-        <v/>
+      <c r="G15" s="11" t="n">
+        <v>0.103</v>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
@@ -4319,13 +4887,11 @@
       <c r="B16" s="10" t="n">
         <v>7259.22</v>
       </c>
-      <c r="C16" s="10">
-        <f>B16-B15</f>
-        <v/>
-      </c>
-      <c r="D16" s="11">
-        <f>(B16-B15)/B15</f>
-        <v/>
+      <c r="C16" s="10" t="n">
+        <v>58.47</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0.0081</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>7197.59</v>
@@ -4333,9 +4899,8 @@
       <c r="F16" s="10" t="n">
         <v>7199.01</v>
       </c>
-      <c r="G16" s="11">
-        <f>(B16-6528.52)/6528.52</f>
-        <v/>
+      <c r="G16" s="11" t="n">
+        <v>0.1119</v>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
@@ -4362,7 +4927,9 @@
       <c r="B17" s="18" t="n">
         <v>7365.12</v>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="n">
+        <v>105.9</v>
+      </c>
       <c r="D17" s="18" t="n">
         <v>0.0146</v>
       </c>
@@ -4400,8 +4967,12 @@
       <c r="B18" s="18" t="n">
         <v>7412</v>
       </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
+      <c r="C18" s="18" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>0.0064</v>
+      </c>
       <c r="E18" s="42" t="n">
         <v>7293.44</v>
       </c>
@@ -4436,8 +5007,12 @@
       <c r="B19" s="18" t="n">
         <v>7501.39</v>
       </c>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
+      <c r="C19" s="18" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>0.0121</v>
+      </c>
       <c r="E19" s="42" t="n">
         <v>7347.7</v>
       </c>
@@ -4472,7 +5047,9 @@
       <c r="B20" s="18" t="n">
         <v>7599.96</v>
       </c>
-      <c r="C20" s="18" t="n"/>
+      <c r="C20" s="18" t="n">
+        <v>98.56999999999999</v>
+      </c>
       <c r="D20" s="18" t="n">
         <v>0.0026</v>
       </c>
@@ -4510,7 +5087,9 @@
       <c r="B21" s="18" t="n">
         <v>7609.78</v>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="n">
+        <v>9.82</v>
+      </c>
       <c r="D21" s="18" t="n">
         <v>0.0013</v>
       </c>
@@ -4548,8 +5127,12 @@
       <c r="B22" s="41" t="n">
         <v>7583.95</v>
       </c>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
+      <c r="C22" s="41" t="n">
+        <v>-25.83</v>
+      </c>
+      <c r="D22" s="45" t="n">
+        <v>-0.0034</v>
+      </c>
       <c r="E22" s="44" t="n">
         <v>7541.42</v>
       </c>
@@ -4584,7 +5167,9 @@
       <c r="B23" s="19" t="n">
         <v>7383.74</v>
       </c>
-      <c r="C23" s="19" t="n"/>
+      <c r="C23" s="19" t="n">
+        <v>-200.21</v>
+      </c>
       <c r="D23" s="19" t="n">
         <v>-0.0264</v>
       </c>
@@ -4902,7 +5487,9 @@
       <c r="B31" s="19" t="n">
         <v>7420.1</v>
       </c>
-      <c r="C31" s="19" t="n"/>
+      <c r="C31" s="19" t="n">
+        <v>-90.88</v>
+      </c>
       <c r="D31" s="19" t="n">
         <v>-0.0121</v>
       </c>
@@ -5140,6 +5727,9 @@
       <c r="B37" t="n">
         <v>7445</v>
       </c>
+      <c r="C37" t="n">
+        <v>87.51000000000001</v>
+      </c>
       <c r="D37" t="n">
         <v>0.012</v>
       </c>
@@ -5217,6 +5807,9 @@
       <c r="B39" t="n">
         <v>7483</v>
       </c>
+      <c r="C39" t="n">
+        <v>33.64</v>
+      </c>
       <c r="D39" t="n">
         <v>0.0045</v>
       </c>
@@ -5254,6 +5847,9 @@
       <c r="B40" t="n">
         <v>7453.96</v>
       </c>
+      <c r="C40" t="n">
+        <v>-29.04</v>
+      </c>
       <c r="D40" t="n">
         <v>-0.0039</v>
       </c>
@@ -5291,7 +5887,9 @@
       <c r="B41" s="41" t="n">
         <v>7537.43</v>
       </c>
-      <c r="C41" s="41" t="n"/>
+      <c r="C41" s="41" t="n">
+        <v>83.47</v>
+      </c>
       <c r="D41" s="41" t="n">
         <v>0.0072</v>
       </c>
@@ -5606,14 +6204,34 @@
           <t>Jul 16</t>
         </is>
       </c>
-      <c r="B49" s="41" t="n"/>
-      <c r="C49" s="41" t="n"/>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C49" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="D49" s="41" t="n">
         <v>-0.0037</v>
       </c>
-      <c r="E49" s="41" t="n"/>
-      <c r="F49" s="41" t="n"/>
-      <c r="G49" s="41" t="n"/>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F49" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G49" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H49" s="41" t="inlineStr">
         <is>
           <t>SELL</t>
@@ -5639,7 +6257,9 @@
       <c r="B50" s="41" t="n">
         <v>7457</v>
       </c>
-      <c r="C50" s="41" t="n"/>
+      <c r="C50" s="41" t="n">
+        <v>-76.77</v>
+      </c>
       <c r="D50" s="41" t="n">
         <v>-0.0102</v>
       </c>
@@ -5674,12 +6294,36 @@
           <t>Jul 20</t>
         </is>
       </c>
-      <c r="B51" s="41" t="n"/>
-      <c r="C51" s="41" t="n"/>
-      <c r="D51" s="41" t="n"/>
-      <c r="E51" s="41" t="n"/>
-      <c r="F51" s="41" t="n"/>
-      <c r="G51" s="41" t="n"/>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C51" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D51" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E51" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F51" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G51" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H51" s="41" t="inlineStr">
         <is>
           <t>SELL</t>
@@ -5707,11 +6351,31 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="C52" s="41" t="n"/>
-      <c r="D52" s="41" t="n"/>
-      <c r="E52" s="41" t="n"/>
-      <c r="F52" s="41" t="n"/>
-      <c r="G52" s="41" t="n"/>
+      <c r="C52" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D52" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E52" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F52" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G52" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H52" s="41" t="inlineStr">
         <is>
           <t>—</t>
@@ -5823,20 +6487,17 @@
       <c r="C5" s="14" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="D5" s="14">
-        <f>C5-B5</f>
-        <v/>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6">
-        <f>(C5-102)/102</f>
-        <v/>
-      </c>
-      <c r="G5" s="6">
-        <f>(C5-65.83)/65.83</f>
-        <v/>
+      <c r="F5" s="6" t="n">
+        <v>-0.0563</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.4623</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -5856,21 +6517,17 @@
       <c r="C6" s="14" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="14">
-        <f>C6-B6</f>
-        <v/>
-      </c>
-      <c r="E6" s="6">
-        <f>(B6-B5)/B5</f>
-        <v/>
-      </c>
-      <c r="F6" s="6">
-        <f>(C6-102)/102</f>
-        <v/>
-      </c>
-      <c r="G6" s="6">
-        <f>(C6-65.83)/65.83</f>
-        <v/>
+      <c r="D6" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-0.0539</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.4659</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -5890,21 +6547,17 @@
       <c r="C7" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="D7" s="14">
-        <f>C7-B7</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>(B7-B6)/B6</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>(C7-102)/102</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>(C7-65.83)/65.83</f>
-        <v/>
+      <c r="D7" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.0588</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.4583</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -5924,21 +6577,17 @@
       <c r="C8" s="14" t="n">
         <v>105.33</v>
       </c>
-      <c r="D8" s="14">
-        <f>C8-B8</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>(B8-B7)/B7</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>(C8-102)/102</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>(C8-65.83)/65.83</f>
-        <v/>
+      <c r="D8" s="14" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -5958,21 +6607,17 @@
       <c r="C9" s="14" t="n">
         <v>105.33</v>
       </c>
-      <c r="D9" s="14">
-        <f>C9-B9</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>(B9-B8)/B8</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>(C9-102)/102</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>(C9-65.83)/65.83</f>
-        <v/>
+      <c r="D9" s="14" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -5992,21 +6637,17 @@
       <c r="C10" s="14" t="n">
         <v>105.2</v>
       </c>
-      <c r="D10" s="14">
-        <f>C10-B10</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>(B10-B9)/B9</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>(C10-102)/102</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>(C10-65.83)/65.83</f>
-        <v/>
+      <c r="D10" s="14" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.5981</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -6026,21 +6667,17 @@
       <c r="C11" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="D11" s="15">
-        <f>C11-B11</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>(B11-B10)/B10</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>(C11-102)/102</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>(C11-65.83)/65.83</f>
-        <v/>
+      <c r="D11" s="15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>0.6254</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -6060,21 +6697,17 @@
       <c r="C12" s="15" t="n">
         <v>108</v>
       </c>
-      <c r="D12" s="15">
-        <f>C12-B12</f>
-        <v/>
-      </c>
-      <c r="E12" s="11">
-        <f>(B12-B11)/B11</f>
-        <v/>
-      </c>
-      <c r="F12" s="11">
-        <f>(C12-102)/102</f>
-        <v/>
-      </c>
-      <c r="G12" s="11">
-        <f>(C12-65.83)/65.83</f>
-        <v/>
+      <c r="D12" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>0.6405999999999999</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -6094,21 +6727,17 @@
       <c r="C13" s="15" t="n">
         <v>108.5</v>
       </c>
-      <c r="D13" s="15">
-        <f>C13-B13</f>
-        <v/>
-      </c>
-      <c r="E13" s="11">
-        <f>(B13-B12)/B12</f>
-        <v/>
-      </c>
-      <c r="F13" s="11">
-        <f>(C13-102)/102</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>(C13-65.83)/65.83</f>
-        <v/>
+      <c r="D13" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>0.6482</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -6128,21 +6757,17 @@
       <c r="C14" s="15" t="n">
         <v>107.8</v>
       </c>
-      <c r="D14" s="15">
-        <f>C14-B14</f>
-        <v/>
-      </c>
-      <c r="E14" s="11">
-        <f>(B14-B13)/B13</f>
-        <v/>
-      </c>
-      <c r="F14" s="11">
-        <f>(C14-102)/102</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
-        <f>(C14-65.83)/65.83</f>
-        <v/>
+      <c r="D14" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>0.6375999999999999</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -6162,21 +6787,17 @@
       <c r="C15" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="D15" s="15">
-        <f>C15-B15</f>
-        <v/>
-      </c>
-      <c r="E15" s="11">
-        <f>(B15-B14)/B14</f>
-        <v/>
-      </c>
-      <c r="F15" s="11">
-        <f>(C15-102)/102</f>
-        <v/>
-      </c>
-      <c r="G15" s="11">
-        <f>(C15-65.83)/65.83</f>
-        <v/>
+      <c r="D15" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>0.6254</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -6196,21 +6817,17 @@
       <c r="C16" s="15" t="n">
         <v>109.87</v>
       </c>
-      <c r="D16" s="15">
-        <f>C16-B16</f>
-        <v/>
-      </c>
-      <c r="E16" s="11">
-        <f>(B16-B15)/B15</f>
-        <v/>
-      </c>
-      <c r="F16" s="11">
-        <f>(C16-102)/102</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>(C16-65.83)/65.83</f>
-        <v/>
+      <c r="D16" s="15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>0.0772</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>0.669</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -6230,21 +6847,17 @@
       <c r="C17" s="15" t="n">
         <v>109.87</v>
       </c>
-      <c r="D17" s="15">
-        <f>C17-B17</f>
-        <v/>
-      </c>
-      <c r="E17" s="11">
-        <f>(B17-B16)/B16</f>
-        <v/>
-      </c>
-      <c r="F17" s="11">
-        <f>(C17-102)/102</f>
-        <v/>
-      </c>
-      <c r="G17" s="11">
-        <f>(C17-65.83)/65.83</f>
-        <v/>
+      <c r="D17" s="15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>0.0772</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>0.669</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -6258,14 +6871,30 @@
           <t>May 15</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n"/>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="C18" s="18" t="n">
         <v>113</v>
       </c>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="G18" s="43" t="n">
+        <v>0.7165</v>
+      </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
           <t>Brent peaks &gt;$113 on Hormuz disruption (2026 high)</t>
@@ -6287,9 +6916,15 @@
       <c r="D19" s="19" t="n">
         <v>3.99</v>
       </c>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="19" t="n"/>
+      <c r="E19" s="47" t="n">
+        <v>-0.0862</v>
+      </c>
+      <c r="F19" s="47" t="n">
+        <v>-0.1377</v>
+      </c>
+      <c r="G19" s="47" t="n">
+        <v>0.4802</v>
+      </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
           <t>Post-gap; premium fading</t>
@@ -6311,9 +6946,15 @@
       <c r="D20" s="19" t="n">
         <v>3.03</v>
       </c>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
-      <c r="G20" s="19" t="n"/>
+      <c r="E20" s="47" t="n">
+        <v>-0.1703</v>
+      </c>
+      <c r="F20" s="47" t="n">
+        <v>-0.287</v>
+      </c>
+      <c r="G20" s="47" t="n">
+        <v>0.2239</v>
+      </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
           <t>Iran re-closed Hormuz; ceasefire tentative</t>
@@ -6335,9 +6976,15 @@
       <c r="D21" s="19" t="n">
         <v>4.11</v>
       </c>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
+      <c r="E21" s="47" t="n">
+        <v>-0.0418</v>
+      </c>
+      <c r="F21" s="47" t="n">
+        <v>-0.3061</v>
+      </c>
+      <c r="G21" s="47" t="n">
+        <v>0.1911</v>
+      </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
           <t>VP Vance 'good foundation'</t>
@@ -6359,9 +7006,15 @@
       <c r="D22" s="19" t="n">
         <v>4.6</v>
       </c>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="19" t="n"/>
-      <c r="G22" s="19" t="n"/>
+      <c r="E22" s="47" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="F22" s="47" t="n">
+        <v>-0.3097</v>
+      </c>
+      <c r="G22" s="47" t="n">
+        <v>0.1849</v>
+      </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
           <t>US 60-day Iran oil waiver; 67M bbls</t>
@@ -6377,11 +7030,29 @@
       <c r="B23" s="19" t="n">
         <v>69.5</v>
       </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E23" s="47" t="n">
+        <v>-0.0531</v>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H23" s="19" t="inlineStr">
         <is>
           <t>WTI &lt;$70 after cargo-ship attack near Oman</t>
@@ -6394,14 +7065,30 @@
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n"/>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="C24" s="19" t="n">
         <v>73.17</v>
       </c>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="19" t="n"/>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F24" s="47" t="n">
+        <v>-0.3525</v>
+      </c>
+      <c r="G24" s="47" t="n">
+        <v>0.1115</v>
+      </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
           <t>Renewed US-Iran strikes</t>
@@ -6423,9 +7110,15 @@
       <c r="D25" s="19" t="n">
         <v>2.99</v>
       </c>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="19" t="n"/>
+      <c r="E25" s="47" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F25" s="47" t="n">
+        <v>-0.0219</v>
+      </c>
+      <c r="G25" s="47" t="n">
+        <v>0.0872</v>
+      </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
           <t>Iran exports surge &gt;40M bbls; &gt;10M bpd via Hormuz</t>
@@ -6447,9 +7140,15 @@
       <c r="D26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="19" t="n"/>
+      <c r="E26" s="47" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F26" s="47" t="n">
+        <v>-0.0707</v>
+      </c>
+      <c r="G26" s="47" t="n">
+        <v>0.033</v>
+      </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
           <t>Crude &lt;$68 (lowest since late Feb); Brent -21% June</t>
@@ -6474,8 +7173,12 @@
       <c r="E27" s="41" t="n">
         <v>0.044</v>
       </c>
-      <c r="F27" s="41" t="n"/>
-      <c r="G27" s="41" t="n"/>
+      <c r="F27" s="45" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="G27" s="45" t="n">
+        <v>0.1852</v>
+      </c>
       <c r="H27" s="41" t="inlineStr">
         <is>
           <t>Trump declares Iran ceasefire over; WTI +4.4%, Brent +5.2%</t>
@@ -6488,12 +7191,36 @@
           <t>Jul 9</t>
         </is>
       </c>
-      <c r="B28" s="41" t="n"/>
-      <c r="C28" s="41" t="n"/>
-      <c r="D28" s="41" t="n"/>
-      <c r="E28" s="41" t="n"/>
-      <c r="F28" s="41" t="n"/>
-      <c r="G28" s="41" t="n"/>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F28" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G28" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H28" s="41" t="inlineStr">
         <is>
           <t>Prices ease after spike; supply-disruption fears persist</t>
@@ -6506,12 +7233,36 @@
           <t>Jul 17</t>
         </is>
       </c>
-      <c r="B29" s="41" t="n"/>
-      <c r="C29" s="41" t="n"/>
-      <c r="D29" s="41" t="n"/>
-      <c r="E29" s="41" t="n"/>
-      <c r="F29" s="41" t="n"/>
-      <c r="G29" s="41" t="n"/>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E29" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F29" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G29" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="H29" s="41" t="inlineStr">
         <is>
           <t>Oil spikes; energy stocks rally as tech routs</t>
@@ -6524,14 +7275,30 @@
           <t>Jul 20</t>
         </is>
       </c>
-      <c r="B30" s="41" t="n"/>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
       <c r="C30" s="41" t="n">
         <v>90</v>
       </c>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="41" t="n"/>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F30" s="45" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G30" s="45" t="n">
+        <v>0.3672</v>
+      </c>
       <c r="H30" s="41" t="inlineStr">
         <is>
           <t>Brent crosses $90 (+30% off July lows); Iran intercepts 4 Hormuz vessels; US resumes blockade</t>
@@ -6772,7 +7539,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~$700B hyperscaler capex</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -6982,7 +7749,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -7318,7 +8085,7 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SOX −10.3%</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
@@ -7486,7 +8253,7 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.25–4.50% target</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -7528,7 +8295,7 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SMH −6.5% / KOSPI −9.99%</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -7696,7 +8463,7 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Best quarter since 2020</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -7780,7 +8547,7 @@
       </c>
       <c r="E32" s="41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>S&amp;P +1.65%</t>
         </is>
       </c>
       <c r="F32" s="41" t="inlineStr">
@@ -7864,7 +8631,7 @@
       </c>
       <c r="E34" s="41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WTI $73.52 / Brent $78.02</t>
         </is>
       </c>
       <c r="F34" s="41" t="inlineStr">
@@ -7906,7 +8673,7 @@
       </c>
       <c r="E35" s="41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Below IPO price</t>
         </is>
       </c>
       <c r="F35" s="41" t="inlineStr">
@@ -7948,7 +8715,7 @@
       </c>
       <c r="E36" s="41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nasdaq week −2.90%</t>
         </is>
       </c>
       <c r="F36" s="41" t="inlineStr">
@@ -8067,7 +8834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.609375" defaultRowHeight="15"/>
   <cols>
     <col width="89.99609375" customWidth="1" style="37" min="1" max="1"/>
@@ -8358,11 +9125,38 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
           <t>- MA/MTD% values computed at finalization (static values; environment could not run a live recalc engine).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Blank-cell fill pass (2026-07-21):</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>- Oil: spread = Brent−WTI; WTI Δ% vs prior LOGGED print; Brent MTD% baselines Apr/102.00, May/107.80 (Apr 30), Jun/113.00 (May 15, last logged), Jul/73.17 (Jun 29, last logged); Brent YoY vs 65.83 constant (original sheet convention).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>- 'n/d' = print not published in available sources — explicitly flagged, never fabricated. '—' = no signal that day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>- S&amp;P Daily Δ / Δ% across source gaps computed vs prior LOGGED close (May 6, May 11, May 14, Jun 4, Jun 5, Jun 17 etc.).</t>
         </is>
       </c>
     </row>
